--- a/data/trending_integrated_20260916_11.xlsx
+++ b/data/trending_integrated_20260916_11.xlsx
@@ -563,31 +563,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>미투온</t>
+          <t>빛샘전자</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3840</v>
+        <v>13910</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+29.95%</t>
+          <t>'+30.00%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-1.21</v>
+        <v>-0.02</v>
       </c>
       <c r="E2" t="n">
-        <v>268</v>
+        <v>65</v>
       </c>
       <c r="F2" t="n">
-        <v>136</v>
+        <v>57</v>
       </c>
       <c r="G2" t="n">
-        <v>847</v>
+        <v>56</v>
       </c>
       <c r="H2" t="n">
-        <v>1.03</v>
+        <v>0.4</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -595,47 +595,47 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>2955</v>
+        <v>10700</v>
       </c>
       <c r="K2" t="n">
-        <v>3840</v>
+        <v>10800</v>
       </c>
       <c r="L2" t="n">
-        <v>3840</v>
+        <v>13910</v>
       </c>
       <c r="M2" t="n">
-        <v>3840</v>
+        <v>10740</v>
       </c>
       <c r="N2" t="n">
-        <v>2.24</v>
+        <v>0.42</v>
       </c>
       <c r="O2" t="n">
-        <v>7115172930</v>
+        <v>159378901740</v>
       </c>
       <c r="P2" t="n">
-        <v>6900</v>
+        <v>25700</v>
       </c>
       <c r="Q2" t="n">
-        <v>1738</v>
+        <v>4600</v>
       </c>
       <c r="R2" t="n">
-        <v>-29000</v>
+        <v>23000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>카카오의 미투온 인수 가능성 및 합법 카지노 사업 확대 기대감. 미버스 코인 급등 언급.</t>
+          <t>6G 통신 대장주로서의 기대감, 광통신, 방산 등 연관 섹터 동반 상승. 강력한 상승 움직임 관찰.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['카카오', '카지노', '인수']</t>
+          <t>['6G', '광통신', '대장주']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -643,43 +643,43 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>201490</t>
+          <t>072950</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>빛샘전자</t>
+          <t>미투온</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13900</v>
+        <v>3840</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+29.91%</t>
+          <t>'+29.95%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.02</v>
+        <v>-1.21</v>
       </c>
       <c r="E3" t="n">
-        <v>61</v>
+        <v>277</v>
       </c>
       <c r="F3" t="n">
-        <v>53</v>
+        <v>137</v>
       </c>
       <c r="G3" t="n">
-        <v>49</v>
+        <v>852</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4</v>
+        <v>1.03</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,47 +687,47 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>10700</v>
+        <v>2955</v>
       </c>
       <c r="K3" t="n">
-        <v>10800</v>
+        <v>3840</v>
       </c>
       <c r="L3" t="n">
-        <v>13910</v>
+        <v>3840</v>
       </c>
       <c r="M3" t="n">
-        <v>10740</v>
+        <v>3840</v>
       </c>
       <c r="N3" t="n">
-        <v>0.42</v>
+        <v>2.24</v>
       </c>
       <c r="O3" t="n">
-        <v>158409111680</v>
+        <v>7123148610</v>
       </c>
       <c r="P3" t="n">
-        <v>25700</v>
+        <v>6900</v>
       </c>
       <c r="Q3" t="n">
-        <v>4600</v>
+        <v>1738</v>
       </c>
       <c r="R3" t="n">
-        <v>23000</v>
+        <v>-29000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>6G 통신 대장주로서의 기대감, 광통신, 방산 등 연관 섹터 동반 상승. 강력한 상승 움직임 관찰.</t>
+          <t>카카오의 미투온 인수 가능성 및 합법 카지노 사업 확대 기대감. 미버스 코인 급등 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['6G', '광통신', '대장주']</t>
+          <t>['카카오', '카지노', '인수']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -735,12 +735,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>072950</t>
+          <t>201490</t>
         </is>
       </c>
     </row>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4620</v>
+        <v>4595</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+12.14%</t>
+          <t>'+11.53%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.03</v>
       </c>
       <c r="E4" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="F4" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G4" t="n">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="H4" t="n">
         <v>0.74</v>
@@ -794,7 +794,7 @@
         <v>0.77</v>
       </c>
       <c r="O4" t="n">
-        <v>261533649695</v>
+        <v>267480266315</v>
       </c>
       <c r="P4" t="n">
         <v>8100</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>AI 데이터센터 투자 수혜 관련 뉴스가 있으나, 급등락 반복 및 '사기 도박판'과 같은 부정적 인식과 함께 뚜렷한 펀더멘탈 근거는 부족함.</t>
+          <t>전일 대비 상승세 및 차트 기반의 긍정적 흐름 관찰, 단기적 상승 기대.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['AI', '데이터센터', '급등락']</t>
+          <t>['차트', '상승', '지지선']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15350</v>
+        <v>15270</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+8.56%</t>
+          <t>'+7.99%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.15</v>
       </c>
       <c r="E5" t="n">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="F5" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G5" t="n">
-        <v>606</v>
+        <v>647</v>
       </c>
       <c r="H5" t="n">
         <v>1.95</v>
@@ -886,7 +886,7 @@
         <v>1.8</v>
       </c>
       <c r="O5" t="n">
-        <v>299499283830</v>
+        <v>308809121240</v>
       </c>
       <c r="P5" t="n">
         <v>31500</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>통신 장비/부품 섹터 강세 및 120일선 돌파 시도 등 긍정적 신호가 나타나고 있으며, 주포의 움직임에 대한 기대감이 높음.</t>
+          <t>통신장비 관련 타 종목 강세 및 차익실현 매물 소화 후 상승 기대감.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['통신장비', '120일선', '주포']</t>
+          <t>['통신장비', '차익실현', '지지선']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3780</v>
+        <v>3785</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+7.54%</t>
+          <t>'+7.68%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.05</v>
       </c>
       <c r="E6" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F6" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G6" t="n">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="H6" t="n">
         <v>3.11</v>
@@ -978,7 +978,7 @@
         <v>3.16</v>
       </c>
       <c r="O6" t="n">
-        <v>12180482760</v>
+        <v>12726724767</v>
       </c>
       <c r="P6" t="n">
         <v>16110</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>25~26년 대규모 적자 및 상폐 가능성 언급 등 재무 건전성에 대한 심각한 우려와 함께 '사기 도박판'이라는 강한 부정적 인식이 지배적임.</t>
+          <t>반복되는 적자 및 재탕 뉴스, 상폐 우려 등 부정적 전망.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['적자', '상폐', '재무']</t>
+          <t>['적자', '상폐', '재탕뉴스']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7330</v>
+        <v>7350</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+6.23%</t>
+          <t>'+6.52%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.09</v>
       </c>
       <c r="E7" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F7" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G7" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="H7" t="n">
         <v>0.79</v>
@@ -1070,7 +1070,7 @@
         <v>0.7</v>
       </c>
       <c r="O7" t="n">
-        <v>68646313035</v>
+        <v>69490044535</v>
       </c>
       <c r="P7" t="n">
         <v>10360</v>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3495</v>
+        <v>3460</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.02%</t>
+          <t>'+2.98%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-1.34</v>
       </c>
       <c r="E8" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F8" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G8" t="n">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1162,7 +1162,7 @@
         <v>1.34</v>
       </c>
       <c r="O8" t="n">
-        <v>86444078574</v>
+        <v>87822432261</v>
       </c>
       <c r="P8" t="n">
         <v>5100</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>190900</v>
+        <v>192000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+2.03%</t>
+          <t>'+2.62%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.01</v>
       </c>
       <c r="E9" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F9" t="n">
         <v>35</v>
       </c>
       <c r="G9" t="n">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="H9" t="n">
         <v>75.66</v>
@@ -1254,7 +1254,7 @@
         <v>75.67</v>
       </c>
       <c r="O9" t="n">
-        <v>351848800900</v>
+        <v>360679066750</v>
       </c>
       <c r="P9" t="n">
         <v>243500</v>
@@ -1299,184 +1299,184 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>한컴위드</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5330</v>
+        <v>1716000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+1.91%</t>
+          <t>'+1.54%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-1.39</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>64</v>
+        <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>41</v>
+        <v>478</v>
       </c>
       <c r="G10" t="n">
-        <v>157</v>
+        <v>2122</v>
       </c>
       <c r="H10" t="n">
-        <v>1.29</v>
+        <v>50.2</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>5230</v>
+        <v>1690000</v>
       </c>
       <c r="K10" t="n">
-        <v>5750</v>
+        <v>1686000</v>
       </c>
       <c r="L10" t="n">
-        <v>5880</v>
+        <v>1731000</v>
       </c>
       <c r="M10" t="n">
-        <v>5200</v>
+        <v>1686000</v>
       </c>
       <c r="N10" t="n">
-        <v>2.68</v>
+        <v>50.27</v>
       </c>
       <c r="O10" t="n">
-        <v>51821291105</v>
+        <v>1734128757500</v>
       </c>
       <c r="P10" t="n">
-        <v>8980</v>
+        <v>2987000</v>
       </c>
       <c r="Q10" t="n">
-        <v>2795</v>
+        <v>331500</v>
       </c>
       <c r="R10" t="n">
-        <v>308000</v>
+        <v>-12000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>미국 보안주 급등, 양자보안 구축 의무화 관련 기대감. 삼성과의 계약 규모에 대한 긍정적 전망 언급.</t>
+          <t>메모리 수요 증가 전망과 자사주 매입/소각 기대감에 따른 긍정적 심리 형성.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['양자보안', '보안주', '계약']</t>
+          <t>['메모리', '자사주매입', '수요']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>2</v>
+        <v>72</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>054920</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>한컴위드</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1712000</v>
+        <v>5300</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+1.30%</t>
+          <t>'+1.34%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-1.39</v>
       </c>
       <c r="E11" t="n">
-        <v>800</v>
+        <v>67</v>
       </c>
       <c r="F11" t="n">
-        <v>475</v>
+        <v>42</v>
       </c>
       <c r="G11" t="n">
-        <v>2157</v>
+        <v>160</v>
       </c>
       <c r="H11" t="n">
-        <v>50.2</v>
+        <v>1.29</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>1690000</v>
+        <v>5230</v>
       </c>
       <c r="K11" t="n">
-        <v>1686000</v>
+        <v>5750</v>
       </c>
       <c r="L11" t="n">
-        <v>1731000</v>
+        <v>5880</v>
       </c>
       <c r="M11" t="n">
-        <v>1686000</v>
+        <v>5200</v>
       </c>
       <c r="N11" t="n">
-        <v>50.27</v>
+        <v>2.68</v>
       </c>
       <c r="O11" t="n">
-        <v>1662395916500</v>
+        <v>52883639305</v>
       </c>
       <c r="P11" t="n">
-        <v>2987000</v>
+        <v>8980</v>
       </c>
       <c r="Q11" t="n">
-        <v>331500</v>
+        <v>2795</v>
       </c>
       <c r="R11" t="n">
-        <v>-12000</v>
+        <v>308000</v>
       </c>
       <c r="S11" t="n">
-        <v>40000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>인텔 CEO 발언, JP모건 매수 등 긍정적 뉴스 및 자사주 매입/소각 기대감으로 인한 상승 전망이 있으나, 금리 인상 등 매크로 지표는 부담 요인.</t>
+          <t>미국 보안주 급등, 양자보안 구축 의무화 관련 기대감. 삼성과의 계약 규모에 대한 긍정적 전망 언급.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['메모리', '자사주매입', '매크로']</t>
+          <t>['양자보안', '보안주', '계약']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>72</v>
+        <v>2</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>054920</t>
         </is>
       </c>
     </row>
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>249250</v>
+        <v>250500</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+0.30%</t>
+          <t>'+0.80%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1501,10 +1501,10 @@
         <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="G12" t="n">
-        <v>2252</v>
+        <v>2121</v>
       </c>
       <c r="H12" t="n">
         <v>46.56</v>
@@ -1530,7 +1530,7 @@
         <v>46.57</v>
       </c>
       <c r="O12" t="n">
-        <v>950695781500</v>
+        <v>996166199250</v>
       </c>
       <c r="P12" t="n">
         <v>374500</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>금리 인상 기대감 및 반도체 섹터 일부 긍정적 뉴스에도 불구하고, 정치적 이슈와 관련된 부정적 내용이 혼재되어 뚜렷한 방향성을 보이지 않음.</t>
+          <t>금리 인상 기대감 속 정치적 이슈 및 지역 기반 반도체 사업 관련 부정적 뉴스 혼재.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['금리인상', '반도체', '정치']</t>
+          <t>['반도체', '금리인상', '정치']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>13260</v>
+        <v>13360</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-0.30%</t>
+          <t>'+0.45%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F13" t="n">
         <v>35</v>
       </c>
       <c r="G13" t="n">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1622,7 +1622,7 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>9817688805</v>
+        <v>10019532215</v>
       </c>
       <c r="P13" t="n">
         <v>19380</v>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10500</v>
+        <v>10480</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-1.50%</t>
+          <t>'-1.69%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>1.29</v>
       </c>
       <c r="E14" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F14" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G14" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="H14" t="n">
         <v>19.22</v>
@@ -1714,7 +1714,7 @@
         <v>17.93</v>
       </c>
       <c r="O14" t="n">
-        <v>90330063385</v>
+        <v>91668389870</v>
       </c>
       <c r="P14" t="n">
         <v>22450</v>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8460</v>
+        <v>8450</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-1.74%</t>
+          <t>'-1.86%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.5</v>
       </c>
       <c r="E15" t="n">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="F15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G15" t="n">
-        <v>262</v>
+        <v>292</v>
       </c>
       <c r="H15" t="n">
         <v>26.66</v>
@@ -1806,7 +1806,7 @@
         <v>27.16</v>
       </c>
       <c r="O15" t="n">
-        <v>8290291475</v>
+        <v>8413378420</v>
       </c>
       <c r="P15" t="n">
         <v>17950</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>낮은 PBR에도 불구하고 부채 문제와 연이은 하락세로 인한 부정적 전망이 지배적이며, 일부 긍정적 수급 신호에도 불구하고 불확실성이 높음.</t>
+          <t>타사 대비 낮은 기업 가치 및 부채 문제, 매수 주체 부재 등으로 인한 부정적 전망.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['PBR', '부채', '수급']</t>
+          <t>['PBR', '부채', '기업가치']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1851,83 +1851,83 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>14680</v>
+        <v>84400</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-2.00%</t>
+          <t>'-2.09%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>-0.08</v>
       </c>
       <c r="E16" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F16" t="n">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="G16" t="n">
-        <v>439</v>
+        <v>574</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>23.37</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>14980</v>
+        <v>86200</v>
       </c>
       <c r="K16" t="n">
-        <v>15300</v>
+        <v>86200</v>
       </c>
       <c r="L16" t="n">
-        <v>15580</v>
+        <v>86300</v>
       </c>
       <c r="M16" t="n">
-        <v>14580</v>
+        <v>83900</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>23.45</v>
       </c>
       <c r="O16" t="n">
-        <v>20965534095</v>
+        <v>71721851650</v>
       </c>
       <c r="P16" t="n">
-        <v>36200</v>
+        <v>139200</v>
       </c>
       <c r="Q16" t="n">
-        <v>8920</v>
+        <v>57000</v>
       </c>
       <c r="R16" t="n">
-        <v>-11000</v>
+        <v>-137000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-5000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>국제유가 상승 및 사우디 관련 이슈로 인한 에너지주 강세 기대감이 있으나, 비축유 방출 및 유가 하락 추세에 대한 우려도 제기. 일부 투자자들은 추가 상승을 기대하며 매수를 이어가고 있으나, 급락 가능성도 언급.</t>
+          <t>웨스팅하우스 지분 인수 및 경영권 참여 가능성에 대한 기대감 상승.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['국제유가', '사우디', '에너지주']</t>
+          <t>['웨스팅하우스', '지분인수', '경영권']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,90 +1936,90 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>84100</v>
+        <v>14660</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-2.44%</t>
+          <t>'-2.14%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.08</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="F17" t="n">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="G17" t="n">
-        <v>551</v>
+        <v>438</v>
       </c>
       <c r="H17" t="n">
-        <v>23.37</v>
+        <v>0</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>86200</v>
+        <v>14980</v>
       </c>
       <c r="K17" t="n">
-        <v>86200</v>
+        <v>15300</v>
       </c>
       <c r="L17" t="n">
-        <v>86300</v>
+        <v>15580</v>
       </c>
       <c r="M17" t="n">
-        <v>83900</v>
+        <v>14580</v>
       </c>
       <c r="N17" t="n">
-        <v>23.45</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>69828918900</v>
+        <v>21376482355</v>
       </c>
       <c r="P17" t="n">
-        <v>139200</v>
+        <v>36200</v>
       </c>
       <c r="Q17" t="n">
-        <v>57000</v>
+        <v>8920</v>
       </c>
       <c r="R17" t="n">
-        <v>-137000</v>
+        <v>-11000</v>
       </c>
       <c r="S17" t="n">
-        <v>-5000</v>
+        <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>웨스팅하우스 지분 인수 관련 뉴스 기반 상승 기대. 공매도 압박 언급.</t>
+          <t>국제 유가 상승 기대감과 에너지주 폭등 가능성 언급. 다만, 비축유 및 유가 하락 추세에 대한 우려와 테마 소멸 가능성 제기.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['웨스팅하우스', '지분 인수', '공매도']</t>
+          <t>['국제유가', '에너지주', '테마']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
@@ -2050,13 +2050,13 @@
         <v>0.1</v>
       </c>
       <c r="E18" t="n">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="F18" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G18" t="n">
-        <v>281</v>
+        <v>294</v>
       </c>
       <c r="H18" t="n">
         <v>0.45</v>
@@ -2082,7 +2082,7 @@
         <v>0.35</v>
       </c>
       <c r="O18" t="n">
-        <v>144869672515</v>
+        <v>146367815285</v>
       </c>
       <c r="P18" t="n">
         <v>30550</v>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>미국 보안주 상승에도 불구하고 상대적 약세에 대한 실망감 표출. 2만원 목표 언급.</t>
+          <t>미국 보안주 상승에 따른 기대감과 개인 물량 털기 의혹, 변동성 심화.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['보안주', '양자', '변동성']</t>
+          <t>['보안주', '변동성', '개미털기']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>18400</v>
+        <v>18430</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-3.82%</t>
+          <t>'-3.66%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0.11</v>
       </c>
       <c r="E19" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F19" t="n">
         <v>51</v>
       </c>
       <c r="G19" t="n">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="H19" t="n">
         <v>10.64</v>
@@ -2174,7 +2174,7 @@
         <v>10.53</v>
       </c>
       <c r="O19" t="n">
-        <v>32830624480</v>
+        <v>33649202755</v>
       </c>
       <c r="P19" t="n">
         <v>40350</v>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>31150</v>
+        <v>31200</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-4.01%</t>
+          <t>'-3.85%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.34</v>
       </c>
       <c r="E20" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F20" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G20" t="n">
-        <v>976</v>
+        <v>996</v>
       </c>
       <c r="H20" t="n">
         <v>17.16</v>
@@ -2266,7 +2266,7 @@
         <v>17.5</v>
       </c>
       <c r="O20" t="n">
-        <v>6101625150</v>
+        <v>6237906100</v>
       </c>
       <c r="P20" t="n">
         <v>69200</v>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5920</v>
+        <v>5880</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-6.18%</t>
+          <t>'-6.81%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>-2.04</v>
       </c>
       <c r="E21" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F21" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G21" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H21" t="n">
         <v>0.98</v>
@@ -2358,7 +2358,7 @@
         <v>3.02</v>
       </c>
       <c r="O21" t="n">
-        <v>38410420035</v>
+        <v>38700184795</v>
       </c>
       <c r="P21" t="n">
         <v>11370</v>
@@ -2379,7 +2379,7 @@
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">

--- a/data/trending_integrated_20260916_11.xlsx
+++ b/data/trending_integrated_20260916_11.xlsx
@@ -578,13 +578,13 @@
         <v>-0.02</v>
       </c>
       <c r="E2" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F2" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G2" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="H2" t="n">
         <v>0.4</v>
@@ -610,7 +610,7 @@
         <v>0.42</v>
       </c>
       <c r="O2" t="n">
-        <v>159378901740</v>
+        <v>159633385190</v>
       </c>
       <c r="P2" t="n">
         <v>25700</v>
@@ -670,13 +670,13 @@
         <v>-1.21</v>
       </c>
       <c r="E3" t="n">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="F3" t="n">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="G3" t="n">
-        <v>852</v>
+        <v>910</v>
       </c>
       <c r="H3" t="n">
         <v>1.03</v>
@@ -702,7 +702,7 @@
         <v>2.24</v>
       </c>
       <c r="O3" t="n">
-        <v>7123148610</v>
+        <v>7137045570</v>
       </c>
       <c r="P3" t="n">
         <v>6900</v>
@@ -751,21 +751,21 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4595</v>
+        <v>4590</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+11.53%</t>
+          <t>'+11.41%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.03</v>
       </c>
       <c r="E4" t="n">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="F4" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G4" t="n">
         <v>153</v>
@@ -794,7 +794,7 @@
         <v>0.77</v>
       </c>
       <c r="O4" t="n">
-        <v>267480266315</v>
+        <v>272018424535</v>
       </c>
       <c r="P4" t="n">
         <v>8100</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>전일 대비 상승세 및 차트 기반의 긍정적 흐름 관찰, 단기적 상승 기대.</t>
+          <t>주가 상승에 대한 기대감과 더불어 적자 지속 및 악질 종목이라는 부정적 언급이 혼재함.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['차트', '상승', '지지선']</t>
+          <t>['상한가', '적자지속', 'AI']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -839,31 +839,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>이뮨온시아</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15270</v>
+        <v>3875</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+7.99%</t>
+          <t>'+10.24%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.15</v>
+        <v>-0.05</v>
       </c>
       <c r="E5" t="n">
-        <v>170</v>
+        <v>98</v>
       </c>
       <c r="F5" t="n">
-        <v>109</v>
+        <v>60</v>
       </c>
       <c r="G5" t="n">
-        <v>647</v>
+        <v>322</v>
       </c>
       <c r="H5" t="n">
-        <v>1.95</v>
+        <v>3.11</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>14140</v>
+        <v>3515</v>
       </c>
       <c r="K5" t="n">
-        <v>14420</v>
+        <v>4120</v>
       </c>
       <c r="L5" t="n">
-        <v>15700</v>
+        <v>4140</v>
       </c>
       <c r="M5" t="n">
-        <v>14300</v>
+        <v>3685</v>
       </c>
       <c r="N5" t="n">
-        <v>1.8</v>
+        <v>3.16</v>
       </c>
       <c r="O5" t="n">
-        <v>308809121240</v>
+        <v>14192164886</v>
       </c>
       <c r="P5" t="n">
-        <v>31500</v>
+        <v>16110</v>
       </c>
       <c r="Q5" t="n">
-        <v>1272</v>
+        <v>2300</v>
       </c>
       <c r="R5" t="n">
-        <v>574000</v>
+        <v>-335000</v>
       </c>
       <c r="S5" t="n">
-        <v>18000</v>
+        <v>-158000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>통신장비 관련 타 종목 강세 및 차익실현 매물 소화 후 상승 기대감.</t>
+          <t>현재 주가 급등에도 불구하고, 최근 2개년의 대규모 적자(각 94억, 95억)로 인한 상장폐지 가능성 제기. 과거 승인 뉴스 재탕 가능성 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['통신장비', '차익실현', '지지선']</t>
+          <t>['적자', '상폐', '공매도']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>424870</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>이뮨온시아</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3785</v>
+        <v>15480</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+7.68%</t>
+          <t>'+9.48%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.05</v>
+        <v>0.15</v>
       </c>
       <c r="E6" t="n">
-        <v>94</v>
+        <v>184</v>
       </c>
       <c r="F6" t="n">
-        <v>59</v>
+        <v>116</v>
       </c>
       <c r="G6" t="n">
-        <v>308</v>
+        <v>672</v>
       </c>
       <c r="H6" t="n">
-        <v>3.11</v>
+        <v>1.95</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,51 +963,51 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>3515</v>
+        <v>14140</v>
       </c>
       <c r="K6" t="n">
-        <v>4120</v>
+        <v>14420</v>
       </c>
       <c r="L6" t="n">
-        <v>4140</v>
+        <v>15700</v>
       </c>
       <c r="M6" t="n">
-        <v>3685</v>
+        <v>14300</v>
       </c>
       <c r="N6" t="n">
-        <v>3.16</v>
+        <v>1.8</v>
       </c>
       <c r="O6" t="n">
-        <v>12726724767</v>
+        <v>320750965785</v>
       </c>
       <c r="P6" t="n">
-        <v>16110</v>
+        <v>31500</v>
       </c>
       <c r="Q6" t="n">
-        <v>2300</v>
+        <v>1272</v>
       </c>
       <c r="R6" t="n">
-        <v>-335000</v>
+        <v>574000</v>
       </c>
       <c r="S6" t="n">
-        <v>-158000</v>
+        <v>18000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>반복되는 적자 및 재탕 뉴스, 상폐 우려 등 부정적 전망.</t>
+          <t>통신 장비 및 부품 섹터의 상승세를 바탕으로 주가 추가 상승에 대한 기대감을 나타냄.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['적자', '상폐', '재탕뉴스']</t>
+          <t>['통신장비', '주포', '거래량']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>424870</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7350</v>
+        <v>7330</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+6.52%</t>
+          <t>'+6.23%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.09</v>
       </c>
       <c r="E7" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F7" t="n">
         <v>38</v>
       </c>
       <c r="G7" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="H7" t="n">
         <v>0.79</v>
@@ -1070,7 +1070,7 @@
         <v>0.7</v>
       </c>
       <c r="O7" t="n">
-        <v>69490044535</v>
+        <v>70009066120</v>
       </c>
       <c r="P7" t="n">
         <v>10360</v>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3460</v>
+        <v>3515</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+2.98%</t>
+          <t>'+4.61%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-1.34</v>
       </c>
       <c r="E8" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F8" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G8" t="n">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1162,7 +1162,7 @@
         <v>1.34</v>
       </c>
       <c r="O8" t="n">
-        <v>87822432261</v>
+        <v>89429691182</v>
       </c>
       <c r="P8" t="n">
         <v>5100</v>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>192000</v>
+        <v>191800</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+2.62%</t>
+          <t>'+2.51%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1228,7 +1228,7 @@
         <v>35</v>
       </c>
       <c r="G9" t="n">
-        <v>183</v>
+        <v>223</v>
       </c>
       <c r="H9" t="n">
         <v>75.66</v>
@@ -1254,7 +1254,7 @@
         <v>75.67</v>
       </c>
       <c r="O9" t="n">
-        <v>360679066750</v>
+        <v>368435123000</v>
       </c>
       <c r="P9" t="n">
         <v>243500</v>
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1716000</v>
+        <v>1714000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+1.54%</t>
+          <t>'+1.42%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1317,10 +1317,10 @@
         <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="G10" t="n">
-        <v>2122</v>
+        <v>2106</v>
       </c>
       <c r="H10" t="n">
         <v>50.2</v>
@@ -1346,7 +1346,7 @@
         <v>50.27</v>
       </c>
       <c r="O10" t="n">
-        <v>1734128757500</v>
+        <v>1788468200000</v>
       </c>
       <c r="P10" t="n">
         <v>2987000</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>메모리 수요 증가 전망과 자사주 매입/소각 기대감에 따른 긍정적 심리 형성.</t>
+          <t>인텔 CEO 발언과 자사주 매입 기대감을 바탕으로 주가 상승 전망을 제시함.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['메모리', '자사주매입', '수요']</t>
+          <t>['자사주매입', '반도체', '매수']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1391,184 +1391,184 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>한컴위드</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5300</v>
+        <v>249750</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+1.34%</t>
+          <t>'+0.50%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-1.39</v>
+        <v>-0.01</v>
       </c>
       <c r="E11" t="n">
-        <v>67</v>
+        <v>800</v>
       </c>
       <c r="F11" t="n">
-        <v>42</v>
+        <v>448</v>
       </c>
       <c r="G11" t="n">
-        <v>160</v>
+        <v>2008</v>
       </c>
       <c r="H11" t="n">
-        <v>1.29</v>
+        <v>46.56</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>5230</v>
+        <v>248500</v>
       </c>
       <c r="K11" t="n">
-        <v>5750</v>
+        <v>248000</v>
       </c>
       <c r="L11" t="n">
-        <v>5880</v>
+        <v>251500</v>
       </c>
       <c r="M11" t="n">
-        <v>5200</v>
+        <v>247500</v>
       </c>
       <c r="N11" t="n">
-        <v>2.68</v>
+        <v>46.57</v>
       </c>
       <c r="O11" t="n">
-        <v>52883639305</v>
+        <v>1047708140750</v>
       </c>
       <c r="P11" t="n">
-        <v>8980</v>
+        <v>374500</v>
       </c>
       <c r="Q11" t="n">
-        <v>2795</v>
+        <v>76700</v>
       </c>
       <c r="R11" t="n">
-        <v>308000</v>
+        <v>-573000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>259000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>미국 보안주 급등, 양자보안 구축 의무화 관련 기대감. 삼성과의 계약 규모에 대한 긍정적 전망 언급.</t>
+          <t>정치적 이슈와 함께 반도체 산업의 전망에 대한 엇갈린 의견이 존재함.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['양자보안', '보안주', '계약']</t>
+          <t>['금리인상', '반도체', '청문회']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>2</v>
+        <v>107</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>054920</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>한컴위드</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>250500</v>
+        <v>5240</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+0.80%</t>
+          <t>'+0.19%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.01</v>
+        <v>-1.39</v>
       </c>
       <c r="E12" t="n">
-        <v>800</v>
+        <v>68</v>
       </c>
       <c r="F12" t="n">
-        <v>453</v>
+        <v>42</v>
       </c>
       <c r="G12" t="n">
-        <v>2121</v>
+        <v>161</v>
       </c>
       <c r="H12" t="n">
-        <v>46.56</v>
+        <v>1.29</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>248500</v>
+        <v>5230</v>
       </c>
       <c r="K12" t="n">
-        <v>248000</v>
+        <v>5750</v>
       </c>
       <c r="L12" t="n">
-        <v>251500</v>
+        <v>5880</v>
       </c>
       <c r="M12" t="n">
-        <v>247500</v>
+        <v>5200</v>
       </c>
       <c r="N12" t="n">
-        <v>46.57</v>
+        <v>2.68</v>
       </c>
       <c r="O12" t="n">
-        <v>996166199250</v>
+        <v>53658002265</v>
       </c>
       <c r="P12" t="n">
-        <v>374500</v>
+        <v>8980</v>
       </c>
       <c r="Q12" t="n">
-        <v>76700</v>
+        <v>2795</v>
       </c>
       <c r="R12" t="n">
-        <v>-573000</v>
+        <v>308000</v>
       </c>
       <c r="S12" t="n">
-        <v>259000</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>금리 인상 기대감 속 정치적 이슈 및 지역 기반 반도체 사업 관련 부정적 뉴스 혼재.</t>
+          <t>미국 보안주 급등, 양자보안 구축 의무화 관련 기대감. 삼성과의 계약 규모에 대한 긍정적 전망 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['반도체', '금리인상', '정치']</t>
+          <t>['양자보안', '보안주', '계약']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>107</v>
+        <v>2</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>054920</t>
         </is>
       </c>
     </row>
@@ -1579,11 +1579,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>13360</v>
+        <v>13300</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+0.45%</t>
+          <t>'+0.00%</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1593,7 +1593,7 @@
         <v>44</v>
       </c>
       <c r="F13" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G13" t="n">
         <v>190</v>
@@ -1622,7 +1622,7 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>10019532215</v>
+        <v>10206030715</v>
       </c>
       <c r="P13" t="n">
         <v>19380</v>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10480</v>
+        <v>10470</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-1.69%</t>
+          <t>'-1.78%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>1.29</v>
       </c>
       <c r="E14" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="F14" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G14" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="H14" t="n">
         <v>19.22</v>
@@ -1714,7 +1714,7 @@
         <v>17.93</v>
       </c>
       <c r="O14" t="n">
-        <v>91668389870</v>
+        <v>93251017610</v>
       </c>
       <c r="P14" t="n">
         <v>22450</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>의미 없는 투자 투주 언급, 거래량 증가 시 20% 상승 가능성 기대. 외인 매수세 유입.</t>
+          <t>개별 종목의 급등 가능성에 대한 기대감을 표출하나, 구체적인 근거는 부족함.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['거래량', '상승', '외인']</t>
+          <t>['거래량', '상승']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
@@ -1774,13 +1774,13 @@
         <v>-0.5</v>
       </c>
       <c r="E15" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="F15" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G15" t="n">
-        <v>292</v>
+        <v>313</v>
       </c>
       <c r="H15" t="n">
         <v>26.66</v>
@@ -1806,7 +1806,7 @@
         <v>27.16</v>
       </c>
       <c r="O15" t="n">
-        <v>8413378420</v>
+        <v>8862372160</v>
       </c>
       <c r="P15" t="n">
         <v>17950</v>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>타사 대비 낮은 기업 가치 및 부채 문제, 매수 주체 부재 등으로 인한 부정적 전망.</t>
+          <t>타 계열사 대비 저평가 및 재무 상태에 대한 우려와 함께 외인 매도세가 관찰됨.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['PBR', '부채', '기업가치']</t>
+          <t>['PBR', '외인매도', '재무']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>84400</v>
+        <v>84500</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-2.09%</t>
+          <t>'-1.97%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-0.08</v>
       </c>
       <c r="E16" t="n">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F16" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G16" t="n">
-        <v>574</v>
+        <v>583</v>
       </c>
       <c r="H16" t="n">
         <v>23.37</v>
@@ -1898,7 +1898,7 @@
         <v>23.45</v>
       </c>
       <c r="O16" t="n">
-        <v>71721851650</v>
+        <v>73255313500</v>
       </c>
       <c r="P16" t="n">
         <v>139200</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>웨스팅하우스 지분 인수 및 경영권 참여 가능성에 대한 기대감 상승.</t>
+          <t>웨스팅하우스 지분 인수 가능성에 대한 기대감과 공매도에 대한 언급이 있음.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['웨스팅하우스', '지분인수', '경영권']</t>
+          <t>['웨스팅하우스', '지분인수', '공매도']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>14660</v>
+        <v>14600</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-2.14%</t>
+          <t>'-2.54%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F17" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G17" t="n">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1990,7 +1990,7 @@
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>21376482355</v>
+        <v>21945946200</v>
       </c>
       <c r="P17" t="n">
         <v>36200</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>국제 유가 상승 기대감과 에너지주 폭등 가능성 언급. 다만, 비축유 및 유가 하락 추세에 대한 우려와 테마 소멸 가능성 제기.</t>
+          <t>국제 유가 상승 및 관련주 폭등을 언급하나, 급락 가능성 및 테마 종료에 대한 우려도 있음.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['국제유가', '에너지주', '테마']</t>
+          <t>['국제유가', '비축유', '테마']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>16990</v>
+        <v>16900</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-3.19%</t>
+          <t>'-3.70%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0.1</v>
       </c>
       <c r="E18" t="n">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="F18" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="G18" t="n">
-        <v>294</v>
+        <v>305</v>
       </c>
       <c r="H18" t="n">
         <v>0.45</v>
@@ -2076,13 +2076,13 @@
         <v>18860</v>
       </c>
       <c r="M18" t="n">
-        <v>16960</v>
+        <v>16900</v>
       </c>
       <c r="N18" t="n">
         <v>0.35</v>
       </c>
       <c r="O18" t="n">
-        <v>146367815285</v>
+        <v>148075364955</v>
       </c>
       <c r="P18" t="n">
         <v>30550</v>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>미국 보안주 상승에 따른 기대감과 개인 물량 털기 의혹, 변동성 심화.</t>
+          <t>미국 보안주 상승과 매출 발생 기업임을 언급하나, 주가 인위적 하락에 대한 불만도 존재함.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['보안주', '변동성', '개미털기']</t>
+          <t>['보안주', '매출', 'VI']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>18430</v>
+        <v>18390</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-3.66%</t>
+          <t>'-3.87%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0.11</v>
       </c>
       <c r="E19" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F19" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G19" t="n">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="H19" t="n">
         <v>10.64</v>
@@ -2174,7 +2174,7 @@
         <v>10.53</v>
       </c>
       <c r="O19" t="n">
-        <v>33649202755</v>
+        <v>34500369635</v>
       </c>
       <c r="P19" t="n">
         <v>40350</v>
@@ -2190,16 +2190,16 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>대차해지 운동 동참 호소. 공매도 종식 및 주가 상승 기대.</t>
+          <t>대차 해지 운동 참여 독려와 함께 주가 상승에 대한 강한 기대감을 보임.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['대차해지', '공매도', '주가 상승']</t>
+          <t>['대차해지', '공매도', '주가조작']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>31200</v>
+        <v>31150</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-3.85%</t>
+          <t>'-4.01%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.34</v>
       </c>
       <c r="E20" t="n">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F20" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G20" t="n">
-        <v>996</v>
+        <v>1012</v>
       </c>
       <c r="H20" t="n">
         <v>17.16</v>
@@ -2266,7 +2266,7 @@
         <v>17.5</v>
       </c>
       <c r="O20" t="n">
-        <v>6237906100</v>
+        <v>6383328350</v>
       </c>
       <c r="P20" t="n">
         <v>69200</v>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>담관암 신약 유럽 신청 등 개발 관련 이슈가 있으나, 과거 신약 실패 이력 및 공모주 청약 이슈로 인한 불확실성과 부정적 전망이 혼재함.</t>
+          <t>간암 신약 실패 이력 기반 하방 베팅 의견. 유럽 담관암 신약 신청 시점에 대한 의문 제기 및 미국 승인 실패 시 주가 하락 가능성 언급.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['담관암', '신약', 'FDA']</t>
+          <t>['간암', '담관암', '신약 신청']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2326,10 +2326,10 @@
         <v>-2.04</v>
       </c>
       <c r="E21" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F21" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G21" t="n">
         <v>150</v>
@@ -2358,7 +2358,7 @@
         <v>3.02</v>
       </c>
       <c r="O21" t="n">
-        <v>38700184795</v>
+        <v>38875897350</v>
       </c>
       <c r="P21" t="n">
         <v>11370</v>

--- a/data/trending_integrated_20260916_11.xlsx
+++ b/data/trending_integrated_20260916_11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z21"/>
+  <dimension ref="A1:Z22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,31 +563,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>빛샘전자</t>
+          <t>미투온</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>13910</v>
+        <v>3840</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+30.00%</t>
+          <t>'+29.95%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.02</v>
+        <v>-1.21</v>
       </c>
       <c r="E2" t="n">
-        <v>66</v>
+        <v>286</v>
       </c>
       <c r="F2" t="n">
-        <v>55</v>
+        <v>141</v>
       </c>
       <c r="G2" t="n">
-        <v>60</v>
+        <v>945</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4</v>
+        <v>1.03</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -595,47 +595,47 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>10700</v>
+        <v>2955</v>
       </c>
       <c r="K2" t="n">
-        <v>10800</v>
+        <v>3840</v>
       </c>
       <c r="L2" t="n">
-        <v>13910</v>
+        <v>3840</v>
       </c>
       <c r="M2" t="n">
-        <v>10740</v>
+        <v>3840</v>
       </c>
       <c r="N2" t="n">
-        <v>0.42</v>
+        <v>2.24</v>
       </c>
       <c r="O2" t="n">
-        <v>159633385190</v>
+        <v>7148047170</v>
       </c>
       <c r="P2" t="n">
-        <v>25700</v>
+        <v>6900</v>
       </c>
       <c r="Q2" t="n">
-        <v>4600</v>
+        <v>1738</v>
       </c>
       <c r="R2" t="n">
-        <v>23000</v>
+        <v>-29000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>6G 통신 대장주로서의 기대감, 광통신, 방산 등 연관 섹터 동반 상승. 강력한 상승 움직임 관찰.</t>
+          <t>카카오의 미투온 인수 관련 카지노 사업 진출 기대감. 클래리티법 부결 영향 미미. 숏커버링 발생 및 미버스코인 급등.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['6G', '광통신', '대장주']</t>
+          <t>['카카오 인수', '카지노', '숏커버링']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -643,43 +643,43 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>072950</t>
+          <t>201490</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>미투온</t>
+          <t>빛샘전자</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3840</v>
+        <v>13540</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+29.95%</t>
+          <t>'+26.54%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-1.21</v>
+        <v>-0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>282</v>
+        <v>65</v>
       </c>
       <c r="F3" t="n">
-        <v>140</v>
+        <v>54</v>
       </c>
       <c r="G3" t="n">
-        <v>910</v>
+        <v>55</v>
       </c>
       <c r="H3" t="n">
-        <v>1.03</v>
+        <v>0.4</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,47 +687,47 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2955</v>
+        <v>10700</v>
       </c>
       <c r="K3" t="n">
-        <v>3840</v>
+        <v>10800</v>
       </c>
       <c r="L3" t="n">
-        <v>3840</v>
+        <v>13910</v>
       </c>
       <c r="M3" t="n">
-        <v>3840</v>
+        <v>10740</v>
       </c>
       <c r="N3" t="n">
-        <v>2.24</v>
+        <v>0.42</v>
       </c>
       <c r="O3" t="n">
-        <v>7137045570</v>
+        <v>163674742980</v>
       </c>
       <c r="P3" t="n">
-        <v>6900</v>
+        <v>25700</v>
       </c>
       <c r="Q3" t="n">
-        <v>1738</v>
+        <v>4600</v>
       </c>
       <c r="R3" t="n">
-        <v>-29000</v>
+        <v>23000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>카카오의 미투온 인수 가능성 및 합법 카지노 사업 확대 기대감. 미버스 코인 급등 언급.</t>
+          <t>6G 통신 대장주로서의 기대감, 광통신, 방산 등 연관 섹터 동반 상승. 강력한 상승 움직임 관찰.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['카카오', '카지노', '인수']</t>
+          <t>['6G', '광통신', '대장주']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -735,43 +735,43 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>201490</t>
+          <t>072950</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4590</v>
+        <v>15860</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+11.41%</t>
+          <t>'+12.16%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.03</v>
+        <v>0.15</v>
       </c>
       <c r="E4" t="n">
-        <v>108</v>
+        <v>194</v>
       </c>
       <c r="F4" t="n">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="G4" t="n">
-        <v>153</v>
+        <v>719</v>
       </c>
       <c r="H4" t="n">
-        <v>0.74</v>
+        <v>1.95</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,51 +779,51 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>4120</v>
+        <v>14140</v>
       </c>
       <c r="K4" t="n">
-        <v>4120</v>
+        <v>14420</v>
       </c>
       <c r="L4" t="n">
-        <v>4800</v>
+        <v>15860</v>
       </c>
       <c r="M4" t="n">
-        <v>4100</v>
+        <v>14300</v>
       </c>
       <c r="N4" t="n">
-        <v>0.77</v>
+        <v>1.8</v>
       </c>
       <c r="O4" t="n">
-        <v>272018424535</v>
+        <v>355410762160</v>
       </c>
       <c r="P4" t="n">
-        <v>8100</v>
+        <v>31500</v>
       </c>
       <c r="Q4" t="n">
-        <v>592</v>
+        <v>1272</v>
       </c>
       <c r="R4" t="n">
-        <v>32000</v>
+        <v>574000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>18000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>주가 상승에 대한 기대감과 더불어 적자 지속 및 악질 종목이라는 부정적 언급이 혼재함.</t>
+          <t>케이엠더블유, RFHIC 등 통신장비 섹터 강세 속 대한광통신 주가 상승 기대감. 14000원 지지선 확보 및 16500원 돌파 시도.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['상한가', '적자지속', 'AI']</t>
+          <t>['통신장비', '지지선', '주가 상승']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>이뮨온시아</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3875</v>
+        <v>4510</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+10.24%</t>
+          <t>'+9.47%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="E5" t="n">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="F5" t="n">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="G5" t="n">
-        <v>322</v>
+        <v>147</v>
       </c>
       <c r="H5" t="n">
-        <v>3.11</v>
+        <v>0.74</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>3515</v>
+        <v>4120</v>
       </c>
       <c r="K5" t="n">
         <v>4120</v>
       </c>
       <c r="L5" t="n">
-        <v>4140</v>
+        <v>4800</v>
       </c>
       <c r="M5" t="n">
-        <v>3685</v>
+        <v>4100</v>
       </c>
       <c r="N5" t="n">
-        <v>3.16</v>
+        <v>0.77</v>
       </c>
       <c r="O5" t="n">
-        <v>14192164886</v>
+        <v>277504832616</v>
       </c>
       <c r="P5" t="n">
-        <v>16110</v>
+        <v>8100</v>
       </c>
       <c r="Q5" t="n">
-        <v>2300</v>
+        <v>592</v>
       </c>
       <c r="R5" t="n">
-        <v>-335000</v>
+        <v>32000</v>
       </c>
       <c r="S5" t="n">
-        <v>-158000</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>현재 주가 급등에도 불구하고, 최근 2개년의 대규모 적자(각 94억, 95억)로 인한 상장폐지 가능성 제기. 과거 승인 뉴스 재탕 가능성 언급.</t>
+          <t>광케이블 관련 미장 상승 및 PS일렉트로닉스의 AI 데이터센터 투자 수혜 언급. 주가 급등락 및 운전대 의혹.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['적자', '상폐', '공매도']</t>
+          <t>['광케이블', 'AI 데이터센터', '주가 급등락']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>424870</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>이뮨온시아</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15480</v>
+        <v>3805</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+9.48%</t>
+          <t>'+8.25%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.15</v>
+        <v>-0.05</v>
       </c>
       <c r="E6" t="n">
-        <v>184</v>
+        <v>100</v>
       </c>
       <c r="F6" t="n">
-        <v>116</v>
+        <v>61</v>
       </c>
       <c r="G6" t="n">
-        <v>672</v>
+        <v>318</v>
       </c>
       <c r="H6" t="n">
-        <v>1.95</v>
+        <v>3.11</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,51 +963,51 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>14140</v>
+        <v>3515</v>
       </c>
       <c r="K6" t="n">
-        <v>14420</v>
+        <v>4120</v>
       </c>
       <c r="L6" t="n">
-        <v>15700</v>
+        <v>4140</v>
       </c>
       <c r="M6" t="n">
-        <v>14300</v>
+        <v>3685</v>
       </c>
       <c r="N6" t="n">
-        <v>1.8</v>
+        <v>3.16</v>
       </c>
       <c r="O6" t="n">
-        <v>320750965785</v>
+        <v>14700002130</v>
       </c>
       <c r="P6" t="n">
-        <v>31500</v>
+        <v>16110</v>
       </c>
       <c r="Q6" t="n">
-        <v>1272</v>
+        <v>2300</v>
       </c>
       <c r="R6" t="n">
-        <v>574000</v>
+        <v>-335000</v>
       </c>
       <c r="S6" t="n">
-        <v>18000</v>
+        <v>-158000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>통신 장비 및 부품 섹터의 상승세를 바탕으로 주가 추가 상승에 대한 기대감을 나타냄.</t>
+          <t>25~26년도 대규모 적자 지속 전망 및 상폐 가능성 제기. 제약주 국룰 언급하며 단기 급등 후 하락 가능성 경고.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['통신장비', '주포', '거래량']</t>
+          <t>['적자 지속', '상폐 가능성', '제약주']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>424870</t>
         </is>
       </c>
     </row>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7330</v>
+        <v>7340</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+6.23%</t>
+          <t>'+6.38%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.09</v>
       </c>
       <c r="E7" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F7" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G7" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H7" t="n">
         <v>0.79</v>
@@ -1070,7 +1070,7 @@
         <v>0.7</v>
       </c>
       <c r="O7" t="n">
-        <v>70009066120</v>
+        <v>70440830880</v>
       </c>
       <c r="P7" t="n">
         <v>10360</v>
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3515</v>
+        <v>3505</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.61%</t>
+          <t>'+4.32%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1133,10 +1133,10 @@
         <v>74</v>
       </c>
       <c r="F8" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G8" t="n">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1162,7 +1162,7 @@
         <v>1.34</v>
       </c>
       <c r="O8" t="n">
-        <v>89429691182</v>
+        <v>90612783492</v>
       </c>
       <c r="P8" t="n">
         <v>5100</v>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>191800</v>
+        <v>192200</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+2.51%</t>
+          <t>'+2.73%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1228,7 +1228,7 @@
         <v>35</v>
       </c>
       <c r="G9" t="n">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="H9" t="n">
         <v>75.66</v>
@@ -1254,7 +1254,7 @@
         <v>75.67</v>
       </c>
       <c r="O9" t="n">
-        <v>368435123000</v>
+        <v>374749922400</v>
       </c>
       <c r="P9" t="n">
         <v>243500</v>
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1714000</v>
+        <v>1718000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+1.42%</t>
+          <t>'+1.66%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1317,10 +1317,10 @@
         <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="G10" t="n">
-        <v>2106</v>
+        <v>2079</v>
       </c>
       <c r="H10" t="n">
         <v>50.2</v>
@@ -1346,7 +1346,7 @@
         <v>50.27</v>
       </c>
       <c r="O10" t="n">
-        <v>1788468200000</v>
+        <v>1874894607000</v>
       </c>
       <c r="P10" t="n">
         <v>2987000</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>인텔 CEO 발언과 자사주 매입 기대감을 바탕으로 주가 상승 전망을 제시함.</t>
+          <t>인텔 CEO 발언 기반 내년 메모리 수요 증가 전망 및 JP모건 SK하이닉스(ADR) 매수 분석. 자사주 매입 및 소각 기대감.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['자사주매입', '반도체', '매수']</t>
+          <t>['메모리 수요', '자사주 매입', 'JP모건']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1391,31 +1391,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>249750</v>
+        <v>10240</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.50%</t>
+          <t>'+1.19%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.01</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>800</v>
+        <v>89</v>
       </c>
       <c r="F11" t="n">
-        <v>448</v>
+        <v>47</v>
       </c>
       <c r="G11" t="n">
-        <v>2008</v>
+        <v>128</v>
       </c>
       <c r="H11" t="n">
-        <v>46.56</v>
+        <v>0.67</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>248500</v>
+        <v>10120</v>
       </c>
       <c r="K11" t="n">
-        <v>248000</v>
+        <v>10190</v>
       </c>
       <c r="L11" t="n">
-        <v>251500</v>
+        <v>10920</v>
       </c>
       <c r="M11" t="n">
-        <v>247500</v>
+        <v>9790</v>
       </c>
       <c r="N11" t="n">
-        <v>46.57</v>
+        <v>0.6</v>
       </c>
       <c r="O11" t="n">
-        <v>1047708140750</v>
+        <v>89258262075</v>
       </c>
       <c r="P11" t="n">
-        <v>374500</v>
+        <v>15960</v>
       </c>
       <c r="Q11" t="n">
-        <v>76700</v>
+        <v>3500</v>
       </c>
       <c r="R11" t="n">
-        <v>-573000</v>
+        <v>-9000</v>
       </c>
       <c r="S11" t="n">
-        <v>259000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>정치적 이슈와 함께 반도체 산업의 전망에 대한 엇갈린 의견이 존재함.</t>
+          <t>미프진 도입 공식화 및 식약처 등록 기대감 속 주가 등락 및 주가 조작 의혹 제기. 해외 불법 암거래 규모 언급.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['금리인상', '반도체', '청문회']</t>
+          <t>['미프진', '식약처', '주가 조작']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>107</v>
+        <v>2</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,169 +1476,169 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>004310</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>한컴위드</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5240</v>
+        <v>251000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+0.19%</t>
+          <t>'+1.01%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-1.39</v>
+        <v>-0.01</v>
       </c>
       <c r="E12" t="n">
-        <v>68</v>
+        <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>42</v>
+        <v>445</v>
       </c>
       <c r="G12" t="n">
-        <v>161</v>
+        <v>1991</v>
       </c>
       <c r="H12" t="n">
-        <v>1.29</v>
+        <v>46.56</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>5230</v>
+        <v>248500</v>
       </c>
       <c r="K12" t="n">
-        <v>5750</v>
+        <v>248000</v>
       </c>
       <c r="L12" t="n">
-        <v>5880</v>
+        <v>251500</v>
       </c>
       <c r="M12" t="n">
-        <v>5200</v>
+        <v>247500</v>
       </c>
       <c r="N12" t="n">
-        <v>2.68</v>
+        <v>46.57</v>
       </c>
       <c r="O12" t="n">
-        <v>53658002265</v>
+        <v>1095122924750</v>
       </c>
       <c r="P12" t="n">
-        <v>8980</v>
+        <v>374500</v>
       </c>
       <c r="Q12" t="n">
-        <v>2795</v>
+        <v>76700</v>
       </c>
       <c r="R12" t="n">
-        <v>308000</v>
+        <v>-573000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>259000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>미국 보안주 급등, 양자보안 구축 의무화 관련 기대감. 삼성과의 계약 규모에 대한 긍정적 전망 언급.</t>
+          <t>금리 인상, 반도체 업황 둔화 우려 속 정치적 이슈 및 인사청문회 관련 논쟁.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['양자보안', '보안주', '계약']</t>
+          <t>['금리인상', '반도체', '업황']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>2</v>
+        <v>107</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>054920</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>한컴위드</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>13300</v>
+        <v>5250</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+0.00%</t>
+          <t>'+0.38%</t>
         </is>
       </c>
       <c r="D13" t="n">
+        <v>-1.39</v>
+      </c>
+      <c r="E13" t="n">
+        <v>67</v>
+      </c>
+      <c r="F13" t="n">
+        <v>41</v>
+      </c>
+      <c r="G13" t="n">
+        <v>161</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>5230</v>
+      </c>
+      <c r="K13" t="n">
+        <v>5750</v>
+      </c>
+      <c r="L13" t="n">
+        <v>5880</v>
+      </c>
+      <c r="M13" t="n">
+        <v>5200</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="O13" t="n">
+        <v>53888409225</v>
+      </c>
+      <c r="P13" t="n">
+        <v>8980</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2795</v>
+      </c>
+      <c r="R13" t="n">
+        <v>308000</v>
+      </c>
+      <c r="S13" t="n">
         <v>0</v>
       </c>
-      <c r="E13" t="n">
-        <v>44</v>
-      </c>
-      <c r="F13" t="n">
-        <v>36</v>
-      </c>
-      <c r="G13" t="n">
-        <v>190</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>MarketType.KOSPI</t>
-        </is>
-      </c>
-      <c r="J13" t="n">
-        <v>13300</v>
-      </c>
-      <c r="K13" t="n">
-        <v>13490</v>
-      </c>
-      <c r="L13" t="n">
-        <v>13940</v>
-      </c>
-      <c r="M13" t="n">
-        <v>13230</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>10206030715</v>
-      </c>
-      <c r="P13" t="n">
-        <v>19380</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>3200</v>
-      </c>
-      <c r="R13" t="n">
-        <v>-22000</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3000</v>
-      </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>주가 하락 및 부진한 흐름에 대한 불만 토로, 영양가 없는 호재 언급. 투자 심리 위축.</t>
+          <t>미국 보안주 급등, 양자보안 구축 의무화 관련 기대감. 삼성과의 계약 규모에 대한 긍정적 전망 언급.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,11 +1647,11 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['주가', '호재', '투자심리']</t>
+          <t>['양자보안', '보안주', '계약']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>54</v>
+        <v>2</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>054920</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10470</v>
+        <v>13310</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-1.78%</t>
+          <t>'+0.08%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="F14" t="n">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="G14" t="n">
-        <v>135</v>
+        <v>201</v>
       </c>
       <c r="H14" t="n">
-        <v>19.22</v>
+        <v>0</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,60 +1699,60 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>10660</v>
+        <v>13300</v>
       </c>
       <c r="K14" t="n">
-        <v>10500</v>
+        <v>13490</v>
       </c>
       <c r="L14" t="n">
-        <v>10900</v>
+        <v>13940</v>
       </c>
       <c r="M14" t="n">
-        <v>10060</v>
+        <v>13230</v>
       </c>
       <c r="N14" t="n">
-        <v>17.93</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>93251017610</v>
+        <v>10409660735</v>
       </c>
       <c r="P14" t="n">
-        <v>22450</v>
+        <v>19380</v>
       </c>
       <c r="Q14" t="n">
-        <v>1760</v>
+        <v>3200</v>
       </c>
       <c r="R14" t="n">
-        <v>-569000</v>
+        <v>-22000</v>
       </c>
       <c r="S14" t="n">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>개별 종목의 급등 가능성에 대한 기대감을 표출하나, 구체적인 근거는 부족함.</t>
+          <t>주가 하락 및 부진한 흐름에 대한 불만 토로, 영양가 없는 호재 언급. 투자 심리 위축.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['거래량', '상승']</t>
+          <t>['주가', '호재', '투자심리']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>3</v>
+        <v>54</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8450</v>
+        <v>8470</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-1.86%</t>
+          <t>'-1.63%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.5</v>
       </c>
       <c r="E15" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F15" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G15" t="n">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="H15" t="n">
         <v>26.66</v>
@@ -1806,7 +1806,7 @@
         <v>27.16</v>
       </c>
       <c r="O15" t="n">
-        <v>8862372160</v>
+        <v>9051817170</v>
       </c>
       <c r="P15" t="n">
         <v>17950</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>타 계열사 대비 저평가 및 재무 상태에 대한 우려와 함께 외인 매도세가 관찰됨.</t>
+          <t>삼성디스플레이 대비 낮은 가치 평가 및 재무 구조 우려. 외인 매도 및 개미 투자자 중심 거래.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['PBR', '외인매도', '재무']</t>
+          <t>['재무 구조', '가치 평가', '외인 매도']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1851,31 +1851,31 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>84500</v>
+        <v>10440</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-1.97%</t>
+          <t>'-2.06%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.08</v>
+        <v>1.29</v>
       </c>
       <c r="E16" t="n">
-        <v>171</v>
+        <v>78</v>
       </c>
       <c r="F16" t="n">
-        <v>108</v>
+        <v>52</v>
       </c>
       <c r="G16" t="n">
-        <v>583</v>
+        <v>133</v>
       </c>
       <c r="H16" t="n">
-        <v>23.37</v>
+        <v>19.22</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,130 +1883,130 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>86200</v>
+        <v>10660</v>
       </c>
       <c r="K16" t="n">
-        <v>86200</v>
+        <v>10500</v>
       </c>
       <c r="L16" t="n">
-        <v>86300</v>
+        <v>10900</v>
       </c>
       <c r="M16" t="n">
-        <v>83900</v>
+        <v>10060</v>
       </c>
       <c r="N16" t="n">
-        <v>23.45</v>
+        <v>17.93</v>
       </c>
       <c r="O16" t="n">
-        <v>73255313500</v>
+        <v>94808711850</v>
       </c>
       <c r="P16" t="n">
-        <v>139200</v>
+        <v>22450</v>
       </c>
       <c r="Q16" t="n">
-        <v>57000</v>
+        <v>1760</v>
       </c>
       <c r="R16" t="n">
-        <v>-137000</v>
+        <v>-569000</v>
       </c>
       <c r="S16" t="n">
-        <v>-5000</v>
+        <v>1000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>웨스팅하우스 지분 인수 가능성에 대한 기대감과 공매도에 대한 언급이 있음.</t>
+          <t>개별 종목의 급등 가능성에 대한 기대감을 표출하나, 구체적인 근거는 부족함.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['웨스팅하우스', '지분인수', '공매도']</t>
+          <t>['거래량', '상승']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>14600</v>
+        <v>84000</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-2.54%</t>
+          <t>'-2.55%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>-0.08</v>
       </c>
       <c r="E17" t="n">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="F17" t="n">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="G17" t="n">
-        <v>443</v>
+        <v>591</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>23.37</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>14980</v>
+        <v>86200</v>
       </c>
       <c r="K17" t="n">
-        <v>15300</v>
+        <v>86200</v>
       </c>
       <c r="L17" t="n">
-        <v>15580</v>
+        <v>86300</v>
       </c>
       <c r="M17" t="n">
-        <v>14580</v>
+        <v>83900</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>23.45</v>
       </c>
       <c r="O17" t="n">
-        <v>21945946200</v>
+        <v>78303972250</v>
       </c>
       <c r="P17" t="n">
-        <v>36200</v>
+        <v>139200</v>
       </c>
       <c r="Q17" t="n">
-        <v>8920</v>
+        <v>57000</v>
       </c>
       <c r="R17" t="n">
-        <v>-11000</v>
+        <v>-137000</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-5000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>국제 유가 상승 및 관련주 폭등을 언급하나, 급락 가능성 및 테마 종료에 대한 우려도 있음.</t>
+          <t>웨스팅하우스 지분 인수 가능성에 대한 기대감과 공매도에 대한 언급이 있음.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,11 +2015,11 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['국제유가', '비축유', '테마']</t>
+          <t>['웨스팅하우스', '지분인수', '공매도']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,38 +2028,38 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>16900</v>
+        <v>14450</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-3.70%</t>
+          <t>'-3.54%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>146</v>
+        <v>185</v>
       </c>
       <c r="F18" t="n">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="G18" t="n">
-        <v>305</v>
+        <v>446</v>
       </c>
       <c r="H18" t="n">
-        <v>0.45</v>
+        <v>0</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,51 +2067,51 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>17550</v>
+        <v>14980</v>
       </c>
       <c r="K18" t="n">
-        <v>17150</v>
+        <v>15300</v>
       </c>
       <c r="L18" t="n">
-        <v>18860</v>
+        <v>15580</v>
       </c>
       <c r="M18" t="n">
-        <v>16900</v>
+        <v>14430</v>
       </c>
       <c r="N18" t="n">
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>148075364955</v>
+        <v>22987454545</v>
       </c>
       <c r="P18" t="n">
-        <v>30550</v>
+        <v>36200</v>
       </c>
       <c r="Q18" t="n">
-        <v>6100</v>
+        <v>8920</v>
       </c>
       <c r="R18" t="n">
-        <v>-60000</v>
+        <v>-11000</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>미국 보안주 상승과 매출 발생 기업임을 언급하나, 주가 인위적 하락에 대한 불만도 존재함.</t>
+          <t>국제 유가 상승 및 관련주 폭등을 언급하나, 급락 가능성 및 테마 종료에 대한 우려도 있음.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['보안주', '매출', 'VI']</t>
+          <t>['국제유가', '비축유', '테마']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
@@ -2131,21 +2131,21 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>18390</v>
+        <v>18420</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-3.87%</t>
+          <t>'-3.71%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0.11</v>
       </c>
       <c r="E19" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F19" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G19" t="n">
         <v>283</v>
@@ -2174,7 +2174,7 @@
         <v>10.53</v>
       </c>
       <c r="O19" t="n">
-        <v>34500369635</v>
+        <v>35379494785</v>
       </c>
       <c r="P19" t="n">
         <v>40350</v>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>31150</v>
+        <v>31200</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-4.01%</t>
+          <t>'-3.85%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.34</v>
       </c>
       <c r="E20" t="n">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="F20" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="G20" t="n">
-        <v>1012</v>
+        <v>1021</v>
       </c>
       <c r="H20" t="n">
         <v>17.16</v>
@@ -2266,7 +2266,7 @@
         <v>17.5</v>
       </c>
       <c r="O20" t="n">
-        <v>6383328350</v>
+        <v>6460395450</v>
       </c>
       <c r="P20" t="n">
         <v>69200</v>
@@ -2311,31 +2311,31 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>아톤</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5880</v>
+        <v>16840</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-6.81%</t>
+          <t>'-4.05%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-2.04</v>
+        <v>0.1</v>
       </c>
       <c r="E21" t="n">
-        <v>82</v>
+        <v>149</v>
       </c>
       <c r="F21" t="n">
-        <v>47</v>
+        <v>84</v>
       </c>
       <c r="G21" t="n">
-        <v>150</v>
+        <v>303</v>
       </c>
       <c r="H21" t="n">
-        <v>0.98</v>
+        <v>0.45</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2343,58 +2343,150 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>6310</v>
+        <v>17550</v>
       </c>
       <c r="K21" t="n">
-        <v>6390</v>
+        <v>17150</v>
       </c>
       <c r="L21" t="n">
-        <v>6450</v>
+        <v>18860</v>
       </c>
       <c r="M21" t="n">
-        <v>5630</v>
+        <v>16800</v>
       </c>
       <c r="N21" t="n">
-        <v>3.02</v>
+        <v>0.35</v>
       </c>
       <c r="O21" t="n">
-        <v>38875897350</v>
+        <v>149869596290</v>
       </c>
       <c r="P21" t="n">
-        <v>11370</v>
+        <v>30550</v>
       </c>
       <c r="Q21" t="n">
-        <v>3300</v>
+        <v>6100</v>
       </c>
       <c r="R21" t="n">
-        <v>389000</v>
+        <v>-60000</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>클래리티법 부결에 따른 영향 분석 및 삼성 계약 언급. 공매도 비중 증가 및 가격 하락 우려.</t>
+          <t>미국 보안주 상승 및 상용화/매출 발생 기업 언급. 개미 털기 위한 주가 인위적 하락 의혹 및 변동성 심화.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['클래리티법', '공매도', '계약']</t>
+          <t>['보안주', '개미털기', '주가 하락']</t>
         </is>
       </c>
       <c r="X21" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>356680</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>아톤</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>5910</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>'-6.34%</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>-2.04</v>
+      </c>
+      <c r="E22" t="n">
+        <v>83</v>
+      </c>
+      <c r="F22" t="n">
+        <v>47</v>
+      </c>
+      <c r="G22" t="n">
+        <v>161</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>6310</v>
+      </c>
+      <c r="K22" t="n">
+        <v>6390</v>
+      </c>
+      <c r="L22" t="n">
+        <v>6450</v>
+      </c>
+      <c r="M22" t="n">
+        <v>5630</v>
+      </c>
+      <c r="N22" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="O22" t="n">
+        <v>39154133945</v>
+      </c>
+      <c r="P22" t="n">
+        <v>11370</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>3300</v>
+      </c>
+      <c r="R22" t="n">
+        <v>389000</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>클래리티법 부결 속 가상자산 규제 입법 지연. 삼성 공급 계약 및 양자보안 샌즈랩 급등. 공매도 증가 및 대규모 장대음봉.</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>['클래리티법', '양자보안', '공매도']</t>
+        </is>
+      </c>
+      <c r="X22" t="n">
         <v>2</v>
       </c>
-      <c r="Y21" t="inlineStr">
+      <c r="Y22" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
+      <c r="Z22" t="inlineStr">
         <is>
           <t>158430</t>
         </is>

--- a/data/trending_integrated_20260916_11.xlsx
+++ b/data/trending_integrated_20260916_11.xlsx
@@ -578,13 +578,13 @@
         <v>-1.21</v>
       </c>
       <c r="E2" t="n">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="F2" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G2" t="n">
-        <v>945</v>
+        <v>982</v>
       </c>
       <c r="H2" t="n">
         <v>1.03</v>
@@ -610,7 +610,7 @@
         <v>2.24</v>
       </c>
       <c r="O2" t="n">
-        <v>7148047170</v>
+        <v>7181950530</v>
       </c>
       <c r="P2" t="n">
         <v>6900</v>
@@ -659,21 +659,21 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13540</v>
+        <v>13740</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+26.54%</t>
+          <t>'+28.41%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="F3" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="G3" t="n">
         <v>55</v>
@@ -702,7 +702,7 @@
         <v>0.42</v>
       </c>
       <c r="O3" t="n">
-        <v>163674742980</v>
+        <v>165771827210</v>
       </c>
       <c r="P3" t="n">
         <v>25700</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15860</v>
+        <v>16440</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+12.16%</t>
+          <t>'+16.27%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.15</v>
       </c>
       <c r="E4" t="n">
-        <v>194</v>
+        <v>231</v>
       </c>
       <c r="F4" t="n">
-        <v>119</v>
+        <v>145</v>
       </c>
       <c r="G4" t="n">
-        <v>719</v>
+        <v>901</v>
       </c>
       <c r="H4" t="n">
         <v>1.95</v>
@@ -785,7 +785,7 @@
         <v>14420</v>
       </c>
       <c r="L4" t="n">
-        <v>15860</v>
+        <v>16500</v>
       </c>
       <c r="M4" t="n">
         <v>14300</v>
@@ -794,7 +794,7 @@
         <v>1.8</v>
       </c>
       <c r="O4" t="n">
-        <v>355410762160</v>
+        <v>419861104100</v>
       </c>
       <c r="P4" t="n">
         <v>31500</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>케이엠더블유, RFHIC 등 통신장비 섹터 강세 속 대한광통신 주가 상승 기대감. 14000원 지지선 확보 및 16500원 돌파 시도.</t>
+          <t>전일 상한가 기록한 빛샘전자 뒤이은 급등세 기대, 통신장비 섹터 강세 및 1.6만원 돌파 전망.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['통신장비', '지지선', '주가 상승']</t>
+          <t>['급등', '통신장비', '상한가']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4510</v>
+        <v>4580</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+9.47%</t>
+          <t>'+11.17%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.03</v>
       </c>
       <c r="E5" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F5" t="n">
         <v>84</v>
       </c>
       <c r="G5" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H5" t="n">
         <v>0.74</v>
@@ -886,7 +886,7 @@
         <v>0.77</v>
       </c>
       <c r="O5" t="n">
-        <v>277504832616</v>
+        <v>283158715790</v>
       </c>
       <c r="P5" t="n">
         <v>8100</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3805</v>
+        <v>3825</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+8.25%</t>
+          <t>'+8.82%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.05</v>
       </c>
       <c r="E6" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F6" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G6" t="n">
-        <v>318</v>
+        <v>339</v>
       </c>
       <c r="H6" t="n">
         <v>3.11</v>
@@ -978,7 +978,7 @@
         <v>3.16</v>
       </c>
       <c r="O6" t="n">
-        <v>14700002130</v>
+        <v>15048585384</v>
       </c>
       <c r="P6" t="n">
         <v>16110</v>
@@ -1023,31 +1023,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>샌즈랩</t>
+          <t>한국첨단소재</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7340</v>
+        <v>3515</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+6.38%</t>
+          <t>'+4.61%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.09</v>
+        <v>-1.34</v>
       </c>
       <c r="E7" t="n">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="F7" t="n">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="G7" t="n">
-        <v>47</v>
+        <v>160</v>
       </c>
       <c r="H7" t="n">
-        <v>0.79</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,38 +1055,38 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>6900</v>
+        <v>3360</v>
       </c>
       <c r="K7" t="n">
-        <v>6770</v>
+        <v>3570</v>
       </c>
       <c r="L7" t="n">
-        <v>8590</v>
+        <v>3910</v>
       </c>
       <c r="M7" t="n">
-        <v>6660</v>
+        <v>3345</v>
       </c>
       <c r="N7" t="n">
-        <v>0.7</v>
+        <v>1.34</v>
       </c>
       <c r="O7" t="n">
-        <v>70440830880</v>
+        <v>91687587074</v>
       </c>
       <c r="P7" t="n">
-        <v>10360</v>
+        <v>5100</v>
       </c>
       <c r="Q7" t="n">
-        <v>2965</v>
+        <v>966</v>
       </c>
       <c r="R7" t="n">
-        <v>87000</v>
+        <v>9000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>보안 대장주로서의 지위 강조 및 AI 관련 논의 언급. 긍정적 흐름 기대.</t>
+          <t>양자내성암호 및 양자보안 관련 글로벌 기업 언급, 한국첨단소재의 독점 공급 기대. 매집 및 이슈 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,11 +1095,11 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['보안주', 'AI', '대장주']</t>
+          <t>['양자암호', '보안', '매집']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>411080</t>
+          <t>062970</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>한국첨단소재</t>
+          <t>샌즈랩</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3505</v>
+        <v>7200</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.32%</t>
+          <t>'+4.35%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-1.34</v>
+        <v>0.09</v>
       </c>
       <c r="E8" t="n">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="F8" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="G8" t="n">
-        <v>159</v>
+        <v>47</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>0.79</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,38 +1147,38 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>3360</v>
+        <v>6900</v>
       </c>
       <c r="K8" t="n">
-        <v>3570</v>
+        <v>6770</v>
       </c>
       <c r="L8" t="n">
-        <v>3910</v>
+        <v>8590</v>
       </c>
       <c r="M8" t="n">
-        <v>3345</v>
+        <v>6660</v>
       </c>
       <c r="N8" t="n">
-        <v>1.34</v>
+        <v>0.7</v>
       </c>
       <c r="O8" t="n">
-        <v>90612783492</v>
+        <v>71273505420</v>
       </c>
       <c r="P8" t="n">
-        <v>5100</v>
+        <v>10360</v>
       </c>
       <c r="Q8" t="n">
-        <v>966</v>
+        <v>2965</v>
       </c>
       <c r="R8" t="n">
-        <v>9000</v>
+        <v>87000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>양자내성암호 및 양자보안 관련 글로벌 기업 언급, 한국첨단소재의 독점 공급 기대. 매집 및 이슈 언급.</t>
+          <t>보안 대장주로서의 지위 강조 및 AI 관련 논의 언급. 긍정적 흐름 기대.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,11 +1187,11 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['양자암호', '보안', '매집']</t>
+          <t>['보안주', 'AI', '대장주']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>062970</t>
+          <t>411080</t>
         </is>
       </c>
     </row>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>192200</v>
+        <v>192500</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+2.73%</t>
+          <t>'+2.89%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.01</v>
       </c>
       <c r="E9" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F9" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G9" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="H9" t="n">
         <v>75.66</v>
@@ -1254,7 +1254,7 @@
         <v>75.67</v>
       </c>
       <c r="O9" t="n">
-        <v>374749922400</v>
+        <v>385399103400</v>
       </c>
       <c r="P9" t="n">
         <v>243500</v>
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1718000</v>
+        <v>1715000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+1.66%</t>
+          <t>'+1.48%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1317,10 +1317,10 @@
         <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="G10" t="n">
-        <v>2079</v>
+        <v>1989</v>
       </c>
       <c r="H10" t="n">
         <v>50.2</v>
@@ -1346,7 +1346,7 @@
         <v>50.27</v>
       </c>
       <c r="O10" t="n">
-        <v>1874894607000</v>
+        <v>1943700295500</v>
       </c>
       <c r="P10" t="n">
         <v>2987000</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>인텔 CEO 발언 기반 내년 메모리 수요 증가 전망 및 JP모건 SK하이닉스(ADR) 매수 분석. 자사주 매입 및 소각 기대감.</t>
+          <t>메모리 수요 증가 및 자사주 매입/소각 기대감 언급, 정치적 이슈와 관련된 부정적 의견 공존.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['메모리 수요', '자사주 매입', 'JP모건']</t>
+          <t>['메모리', '자사주매입', '자사주소각']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1391,31 +1391,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>10240</v>
+        <v>10780</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+1.19%</t>
+          <t>'+1.13%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.07000000000000001</v>
+        <v>1.29</v>
       </c>
       <c r="E11" t="n">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F11" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="G11" t="n">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="H11" t="n">
-        <v>0.67</v>
+        <v>19.22</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,38 +1423,38 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>10120</v>
+        <v>10660</v>
       </c>
       <c r="K11" t="n">
-        <v>10190</v>
+        <v>10500</v>
       </c>
       <c r="L11" t="n">
-        <v>10920</v>
+        <v>10900</v>
       </c>
       <c r="M11" t="n">
-        <v>9790</v>
+        <v>10060</v>
       </c>
       <c r="N11" t="n">
-        <v>0.6</v>
+        <v>17.93</v>
       </c>
       <c r="O11" t="n">
-        <v>89258262075</v>
+        <v>102059710870</v>
       </c>
       <c r="P11" t="n">
-        <v>15960</v>
+        <v>22450</v>
       </c>
       <c r="Q11" t="n">
-        <v>3500</v>
+        <v>1760</v>
       </c>
       <c r="R11" t="n">
-        <v>-9000</v>
+        <v>-569000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>미프진 도입 공식화 및 식약처 등록 기대감 속 주가 등락 및 주가 조작 의혹 제기. 해외 불법 암거래 규모 언급.</t>
+          <t>기대 거래량 충족 시 20% 상승 전망, 단기 급등 가능성 언급.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['미프진', '식약처', '주가 조작']</t>
+          <t>['거래량', '상승', '차트']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>004310</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>251000</v>
+        <v>10220</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+1.01%</t>
+          <t>'+0.99%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.01</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>800</v>
+        <v>92</v>
       </c>
       <c r="F12" t="n">
-        <v>445</v>
+        <v>56</v>
       </c>
       <c r="G12" t="n">
-        <v>1991</v>
+        <v>178</v>
       </c>
       <c r="H12" t="n">
-        <v>46.56</v>
+        <v>0.67</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>248500</v>
+        <v>10120</v>
       </c>
       <c r="K12" t="n">
-        <v>248000</v>
+        <v>10190</v>
       </c>
       <c r="L12" t="n">
-        <v>251500</v>
+        <v>10920</v>
       </c>
       <c r="M12" t="n">
-        <v>247500</v>
+        <v>9790</v>
       </c>
       <c r="N12" t="n">
-        <v>46.57</v>
+        <v>0.6</v>
       </c>
       <c r="O12" t="n">
-        <v>1095122924750</v>
+        <v>93471425045</v>
       </c>
       <c r="P12" t="n">
-        <v>374500</v>
+        <v>15960</v>
       </c>
       <c r="Q12" t="n">
-        <v>76700</v>
+        <v>3500</v>
       </c>
       <c r="R12" t="n">
-        <v>-573000</v>
+        <v>-9000</v>
       </c>
       <c r="S12" t="n">
-        <v>259000</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>금리 인상, 반도체 업황 둔화 우려 속 정치적 이슈 및 인사청문회 관련 논쟁.</t>
+          <t>미프진 도입 공식화 관련 재료 소멸 가능성 및 주가 조작 의혹 제기, 단기 반등 기대.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['금리인상', '반도체', '업황']</t>
+          <t>['미프진', '재료소멸', '주가조작']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>107</v>
+        <v>2</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,99 +1568,99 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>004310</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>한컴위드</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5250</v>
+        <v>250750</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+0.38%</t>
+          <t>'+0.91%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-1.39</v>
+        <v>-0.01</v>
       </c>
       <c r="E13" t="n">
-        <v>67</v>
+        <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>41</v>
+        <v>454</v>
       </c>
       <c r="G13" t="n">
-        <v>161</v>
+        <v>1966</v>
       </c>
       <c r="H13" t="n">
-        <v>1.29</v>
+        <v>46.56</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>5230</v>
+        <v>248500</v>
       </c>
       <c r="K13" t="n">
-        <v>5750</v>
+        <v>248000</v>
       </c>
       <c r="L13" t="n">
-        <v>5880</v>
+        <v>251500</v>
       </c>
       <c r="M13" t="n">
-        <v>5200</v>
+        <v>247500</v>
       </c>
       <c r="N13" t="n">
-        <v>2.68</v>
+        <v>46.57</v>
       </c>
       <c r="O13" t="n">
-        <v>53888409225</v>
+        <v>1128130716500</v>
       </c>
       <c r="P13" t="n">
-        <v>8980</v>
+        <v>374500</v>
       </c>
       <c r="Q13" t="n">
-        <v>2795</v>
+        <v>76700</v>
       </c>
       <c r="R13" t="n">
-        <v>308000</v>
+        <v>-573000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>259000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>미국 보안주 급등, 양자보안 구축 의무화 관련 기대감. 삼성과의 계약 규모에 대한 긍정적 전망 언급.</t>
+          <t>금리인상 및 반도체 업황 관련 내용 혼재, 정치적 이슈와 연관된 부정적 의견 다수.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['양자보안', '보안주', '계약']</t>
+          <t>['금리인상', '반도체', '업황']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>2</v>
+        <v>107</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>054920</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>13310</v>
+        <v>13280</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+0.08%</t>
+          <t>'-0.15%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F14" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G14" t="n">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1714,7 +1714,7 @@
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>10409660735</v>
+        <v>10573704265</v>
       </c>
       <c r="P14" t="n">
         <v>19380</v>
@@ -1759,123 +1759,123 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>한컴위드</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8470</v>
+        <v>5210</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-1.63%</t>
+          <t>'-0.38%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.5</v>
+        <v>-1.39</v>
       </c>
       <c r="E15" t="n">
-        <v>103</v>
+        <v>69</v>
       </c>
       <c r="F15" t="n">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="G15" t="n">
-        <v>322</v>
+        <v>165</v>
       </c>
       <c r="H15" t="n">
-        <v>26.66</v>
+        <v>1.29</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>8610</v>
+        <v>5230</v>
       </c>
       <c r="K15" t="n">
-        <v>8600</v>
+        <v>5750</v>
       </c>
       <c r="L15" t="n">
-        <v>8610</v>
+        <v>5880</v>
       </c>
       <c r="M15" t="n">
-        <v>8430</v>
+        <v>5160</v>
       </c>
       <c r="N15" t="n">
-        <v>27.16</v>
+        <v>2.68</v>
       </c>
       <c r="O15" t="n">
-        <v>9051817170</v>
+        <v>54929468400</v>
       </c>
       <c r="P15" t="n">
-        <v>17950</v>
+        <v>8980</v>
       </c>
       <c r="Q15" t="n">
-        <v>8120</v>
+        <v>2795</v>
       </c>
       <c r="R15" t="n">
-        <v>-528000</v>
+        <v>308000</v>
       </c>
       <c r="S15" t="n">
-        <v>-36000</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>삼성디스플레이 대비 낮은 가치 평가 및 재무 구조 우려. 외인 매도 및 개미 투자자 중심 거래.</t>
+          <t>미국 보안주 급등, 양자보안 구축 의무화 관련 기대감. 삼성과의 계약 규모에 대한 긍정적 전망 언급.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['재무 구조', '가치 평가', '외인 매도']</t>
+          <t>['양자보안', '보안주', '계약']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>054920</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>10440</v>
+        <v>8470</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-2.06%</t>
+          <t>'-1.63%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1.29</v>
+        <v>-0.5</v>
       </c>
       <c r="E16" t="n">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="F16" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G16" t="n">
-        <v>133</v>
+        <v>335</v>
       </c>
       <c r="H16" t="n">
-        <v>19.22</v>
+        <v>26.66</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,60 +1883,60 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>10660</v>
+        <v>8610</v>
       </c>
       <c r="K16" t="n">
-        <v>10500</v>
+        <v>8600</v>
       </c>
       <c r="L16" t="n">
-        <v>10900</v>
+        <v>8610</v>
       </c>
       <c r="M16" t="n">
-        <v>10060</v>
+        <v>8430</v>
       </c>
       <c r="N16" t="n">
-        <v>17.93</v>
+        <v>27.16</v>
       </c>
       <c r="O16" t="n">
-        <v>94808711850</v>
+        <v>9206304240</v>
       </c>
       <c r="P16" t="n">
-        <v>22450</v>
+        <v>17950</v>
       </c>
       <c r="Q16" t="n">
-        <v>1760</v>
+        <v>8120</v>
       </c>
       <c r="R16" t="n">
-        <v>-569000</v>
+        <v>-528000</v>
       </c>
       <c r="S16" t="n">
-        <v>1000</v>
+        <v>-36000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>개별 종목의 급등 가능성에 대한 기대감을 표출하나, 구체적인 근거는 부족함.</t>
+          <t>삼성디스플레이와 비교하며 실적 부진 지적, 대규모 부채 및 개미 투자자 매수세 우려.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['거래량', '상승']</t>
+          <t>['실적', '부채', '개미']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>84000</v>
+        <v>83900</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-2.55%</t>
+          <t>'-2.67%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.08</v>
       </c>
       <c r="E17" t="n">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="F17" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G17" t="n">
-        <v>591</v>
+        <v>608</v>
       </c>
       <c r="H17" t="n">
         <v>23.37</v>
@@ -1984,13 +1984,13 @@
         <v>86300</v>
       </c>
       <c r="M17" t="n">
-        <v>83900</v>
+        <v>83800</v>
       </c>
       <c r="N17" t="n">
         <v>23.45</v>
       </c>
       <c r="O17" t="n">
-        <v>78303972250</v>
+        <v>86482308100</v>
       </c>
       <c r="P17" t="n">
         <v>139200</v>
@@ -2035,31 +2035,31 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>14450</v>
+        <v>16990</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-3.54%</t>
+          <t>'-3.19%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="E18" t="n">
-        <v>185</v>
+        <v>157</v>
       </c>
       <c r="F18" t="n">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="G18" t="n">
-        <v>446</v>
+        <v>302</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,51 +2067,51 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>14980</v>
+        <v>17550</v>
       </c>
       <c r="K18" t="n">
-        <v>15300</v>
+        <v>17150</v>
       </c>
       <c r="L18" t="n">
-        <v>15580</v>
+        <v>18860</v>
       </c>
       <c r="M18" t="n">
-        <v>14430</v>
+        <v>16710</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="O18" t="n">
-        <v>22987454545</v>
+        <v>152439919285</v>
       </c>
       <c r="P18" t="n">
-        <v>36200</v>
+        <v>30550</v>
       </c>
       <c r="Q18" t="n">
-        <v>8920</v>
+        <v>6100</v>
       </c>
       <c r="R18" t="n">
-        <v>-11000</v>
+        <v>-60000</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>국제 유가 상승 및 관련주 폭등을 언급하나, 급락 가능성 및 테마 종료에 대한 우려도 있음.</t>
+          <t>미국 보안주 상승 및 상용화/매출 발생 기업 언급. 개미 털기 위한 주가 인위적 하락 의혹 및 변동성 심화.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['국제유가', '비축유', '테마']</t>
+          <t>['보안주', '개미털기', '주가 하락']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>18420</v>
+        <v>18440</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-3.71%</t>
+          <t>'-3.61%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0.11</v>
       </c>
       <c r="E19" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F19" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G19" t="n">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="H19" t="n">
         <v>10.64</v>
@@ -2174,7 +2174,7 @@
         <v>10.53</v>
       </c>
       <c r="O19" t="n">
-        <v>35379494785</v>
+        <v>37450063845</v>
       </c>
       <c r="P19" t="n">
         <v>40350</v>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>대차 해지 운동 참여 독려와 함께 주가 상승에 대한 강한 기대감을 보임.</t>
+          <t>대차해지 운동 독려하며 공매도 세력과의 갈등 부각, 대형 계약 임박 및 주가 급등 기대.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['대차해지', '공매도', '주가조작']</t>
+          <t>['대차해지', '공매도', '대형계약']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>31200</v>
+        <v>31250</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-3.85%</t>
+          <t>'-3.70%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.34</v>
       </c>
       <c r="E20" t="n">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="F20" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G20" t="n">
-        <v>1021</v>
+        <v>1027</v>
       </c>
       <c r="H20" t="n">
         <v>17.16</v>
@@ -2266,7 +2266,7 @@
         <v>17.5</v>
       </c>
       <c r="O20" t="n">
-        <v>6460395450</v>
+        <v>6798095300</v>
       </c>
       <c r="P20" t="n">
         <v>69200</v>
@@ -2311,31 +2311,31 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>16840</v>
+        <v>14180</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-4.05%</t>
+          <t>'-5.34%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>149</v>
+        <v>196</v>
       </c>
       <c r="F21" t="n">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="G21" t="n">
-        <v>303</v>
+        <v>448</v>
       </c>
       <c r="H21" t="n">
-        <v>0.45</v>
+        <v>0</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2343,51 +2343,51 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>17550</v>
+        <v>14980</v>
       </c>
       <c r="K21" t="n">
-        <v>17150</v>
+        <v>15300</v>
       </c>
       <c r="L21" t="n">
-        <v>18860</v>
+        <v>15580</v>
       </c>
       <c r="M21" t="n">
-        <v>16800</v>
+        <v>14140</v>
       </c>
       <c r="N21" t="n">
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>149869596290</v>
+        <v>24847806270</v>
       </c>
       <c r="P21" t="n">
-        <v>30550</v>
+        <v>36200</v>
       </c>
       <c r="Q21" t="n">
-        <v>6100</v>
+        <v>8920</v>
       </c>
       <c r="R21" t="n">
-        <v>-60000</v>
+        <v>-11000</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>미국 보안주 상승 및 상용화/매출 발생 기업 언급. 개미 털기 위한 주가 인위적 하락 의혹 및 변동성 심화.</t>
+          <t>국제유가 상승 및 지정학적 리스크 부각, 단기 급등 가능성 언급하나 차익 실현 및 급락 우려 상존.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['보안주', '개미털기', '주가 하락']</t>
+          <t>['국제유가', '지정학적리스크', '급등']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5910</v>
+        <v>5870</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-6.34%</t>
+          <t>'-6.97%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>-2.04</v>
       </c>
       <c r="E22" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F22" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G22" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H22" t="n">
         <v>0.98</v>
@@ -2450,7 +2450,7 @@
         <v>3.02</v>
       </c>
       <c r="O22" t="n">
-        <v>39154133945</v>
+        <v>39467572245</v>
       </c>
       <c r="P22" t="n">
         <v>11370</v>

--- a/data/trending_integrated_20260916_11.xlsx
+++ b/data/trending_integrated_20260916_11.xlsx
@@ -578,13 +578,13 @@
         <v>-1.21</v>
       </c>
       <c r="E2" t="n">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F2" t="n">
         <v>142</v>
       </c>
       <c r="G2" t="n">
-        <v>982</v>
+        <v>988</v>
       </c>
       <c r="H2" t="n">
         <v>1.03</v>
@@ -610,7 +610,7 @@
         <v>2.24</v>
       </c>
       <c r="O2" t="n">
-        <v>7181950530</v>
+        <v>7188958530</v>
       </c>
       <c r="P2" t="n">
         <v>6900</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13740</v>
+        <v>13640</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+28.41%</t>
+          <t>'+27.48%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F3" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="G3" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H3" t="n">
         <v>0.4</v>
@@ -702,7 +702,7 @@
         <v>0.42</v>
       </c>
       <c r="O3" t="n">
-        <v>165771827210</v>
+        <v>166486799025</v>
       </c>
       <c r="P3" t="n">
         <v>25700</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16440</v>
+        <v>16040</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+16.27%</t>
+          <t>'+13.44%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.15</v>
       </c>
       <c r="E4" t="n">
-        <v>231</v>
+        <v>258</v>
       </c>
       <c r="F4" t="n">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="G4" t="n">
-        <v>901</v>
+        <v>1011</v>
       </c>
       <c r="H4" t="n">
         <v>1.95</v>
@@ -794,7 +794,7 @@
         <v>1.8</v>
       </c>
       <c r="O4" t="n">
-        <v>419861104100</v>
+        <v>451477355685</v>
       </c>
       <c r="P4" t="n">
         <v>31500</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>전일 상한가 기록한 빛샘전자 뒤이은 급등세 기대, 통신장비 섹터 강세 및 1.6만원 돌파 전망.</t>
+          <t>케이엠더블유, RFHIC 등 통신장비주 강세에 따른 대한광통신의 1.6만원 돌파 및 우상향 추세 전망. 대량 매집 확인 및 10만원 목표 제시.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['급등', '통신장비', '상한가']</t>
+          <t>['통신장비', '우상향', '대량매집']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4580</v>
+        <v>4545</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+11.17%</t>
+          <t>'+10.32%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.03</v>
       </c>
       <c r="E5" t="n">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="F5" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="G5" t="n">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="H5" t="n">
         <v>0.74</v>
@@ -886,7 +886,7 @@
         <v>0.77</v>
       </c>
       <c r="O5" t="n">
-        <v>283158715790</v>
+        <v>285817561300</v>
       </c>
       <c r="P5" t="n">
         <v>8100</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>광케이블 관련 미장 상승 및 PS일렉트로닉스의 AI 데이터센터 투자 수혜 언급. 주가 급등락 및 운전대 의혹.</t>
+          <t>전날 광케이블 상승에 따른 기대감 속 거래량 급증 및 상한가 터치 가능성 언급. 다만 적자 지속 리스크와 외국인 매도세로 인한 하락 가능성도 제기.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['광케이블', 'AI 데이터센터', '주가 급등락']</t>
+          <t>['거래량', '적자지속', '외국인']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3825</v>
+        <v>3775</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+8.82%</t>
+          <t>'+7.40%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.05</v>
       </c>
       <c r="E6" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F6" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G6" t="n">
-        <v>339</v>
+        <v>359</v>
       </c>
       <c r="H6" t="n">
         <v>3.11</v>
@@ -978,7 +978,7 @@
         <v>3.16</v>
       </c>
       <c r="O6" t="n">
-        <v>15048585384</v>
+        <v>15273889814</v>
       </c>
       <c r="P6" t="n">
         <v>16110</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>25~26년도 대규모 적자 지속 전망 및 상폐 가능성 제기. 제약주 국룰 언급하며 단기 급등 후 하락 가능성 경고.</t>
+          <t>25년, 26년 대규모 적자 전망으로 인한 상폐 가능성 및 주가 하락 경고. 임상 1상b 관련 뉴스가 재탕이며, 공매도 세력의 개입 가능성 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['적자 지속', '상폐 가능성', '제약주']</t>
+          <t>['적자', '상폐', '공매도']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1023,31 +1023,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>한국첨단소재</t>
+          <t>샌즈랩</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3515</v>
+        <v>7320</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+4.61%</t>
+          <t>'+6.09%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-1.34</v>
+        <v>0.09</v>
       </c>
       <c r="E7" t="n">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="F7" t="n">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="G7" t="n">
-        <v>160</v>
+        <v>47</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>0.79</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,38 +1055,38 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>3360</v>
+        <v>6900</v>
       </c>
       <c r="K7" t="n">
-        <v>3570</v>
+        <v>6770</v>
       </c>
       <c r="L7" t="n">
-        <v>3910</v>
+        <v>8590</v>
       </c>
       <c r="M7" t="n">
-        <v>3345</v>
+        <v>6660</v>
       </c>
       <c r="N7" t="n">
-        <v>1.34</v>
+        <v>0.7</v>
       </c>
       <c r="O7" t="n">
-        <v>91687587074</v>
+        <v>72497930000</v>
       </c>
       <c r="P7" t="n">
-        <v>5100</v>
+        <v>10360</v>
       </c>
       <c r="Q7" t="n">
-        <v>966</v>
+        <v>2965</v>
       </c>
       <c r="R7" t="n">
-        <v>9000</v>
+        <v>87000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>양자내성암호 및 양자보안 관련 글로벌 기업 언급, 한국첨단소재의 독점 공급 기대. 매집 및 이슈 언급.</t>
+          <t>보안 대장주로서의 지위 강조 및 AI 관련 논의 언급. 긍정적 흐름 기대.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,11 +1095,11 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['양자암호', '보안', '매집']</t>
+          <t>['보안주', 'AI', '대장주']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>062970</t>
+          <t>411080</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>샌즈랩</t>
+          <t>한국첨단소재</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7200</v>
+        <v>3535</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.35%</t>
+          <t>'+5.21%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.09</v>
+        <v>-1.34</v>
       </c>
       <c r="E8" t="n">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="F8" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="G8" t="n">
-        <v>47</v>
+        <v>163</v>
       </c>
       <c r="H8" t="n">
-        <v>0.79</v>
+        <v>0</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,38 +1147,38 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>6900</v>
+        <v>3360</v>
       </c>
       <c r="K8" t="n">
-        <v>6770</v>
+        <v>3570</v>
       </c>
       <c r="L8" t="n">
-        <v>8590</v>
+        <v>3910</v>
       </c>
       <c r="M8" t="n">
-        <v>6660</v>
+        <v>3345</v>
       </c>
       <c r="N8" t="n">
-        <v>0.7</v>
+        <v>1.34</v>
       </c>
       <c r="O8" t="n">
-        <v>71273505420</v>
+        <v>92713658542</v>
       </c>
       <c r="P8" t="n">
-        <v>10360</v>
+        <v>5100</v>
       </c>
       <c r="Q8" t="n">
-        <v>2965</v>
+        <v>966</v>
       </c>
       <c r="R8" t="n">
-        <v>87000</v>
+        <v>9000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>보안 대장주로서의 지위 강조 및 AI 관련 논의 언급. 긍정적 흐름 기대.</t>
+          <t>양자내성암호 및 양자보안 관련 글로벌 기업 언급, 한국첨단소재의 독점 공급 기대. 매집 및 이슈 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,11 +1187,11 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['보안주', 'AI', '대장주']</t>
+          <t>['양자암호', '보안', '매집']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>411080</t>
+          <t>062970</t>
         </is>
       </c>
     </row>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>192500</v>
+        <v>193100</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+2.89%</t>
+          <t>'+3.21%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1228,7 +1228,7 @@
         <v>37</v>
       </c>
       <c r="G9" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H9" t="n">
         <v>75.66</v>
@@ -1254,7 +1254,7 @@
         <v>75.67</v>
       </c>
       <c r="O9" t="n">
-        <v>385399103400</v>
+        <v>392841871900</v>
       </c>
       <c r="P9" t="n">
         <v>243500</v>
@@ -1299,31 +1299,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1715000</v>
+        <v>10310</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+1.48%</t>
+          <t>'+1.88%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>800</v>
+        <v>96</v>
       </c>
       <c r="F10" t="n">
-        <v>474</v>
+        <v>59</v>
       </c>
       <c r="G10" t="n">
-        <v>1989</v>
+        <v>193</v>
       </c>
       <c r="H10" t="n">
-        <v>50.2</v>
+        <v>0.67</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1690000</v>
+        <v>10120</v>
       </c>
       <c r="K10" t="n">
-        <v>1686000</v>
+        <v>10190</v>
       </c>
       <c r="L10" t="n">
-        <v>1731000</v>
+        <v>10920</v>
       </c>
       <c r="M10" t="n">
-        <v>1686000</v>
+        <v>9790</v>
       </c>
       <c r="N10" t="n">
-        <v>50.27</v>
+        <v>0.6</v>
       </c>
       <c r="O10" t="n">
-        <v>1943700295500</v>
+        <v>95458399550</v>
       </c>
       <c r="P10" t="n">
-        <v>2987000</v>
+        <v>15960</v>
       </c>
       <c r="Q10" t="n">
-        <v>331500</v>
+        <v>3500</v>
       </c>
       <c r="R10" t="n">
-        <v>-12000</v>
+        <v>-9000</v>
       </c>
       <c r="S10" t="n">
-        <v>40000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>메모리 수요 증가 및 자사주 매입/소각 기대감 언급, 정치적 이슈와 관련된 부정적 의견 공존.</t>
+          <t>주가 조작 의혹 속 미프진 도입 공식화 및 식약처 등록 가능성 언급. 불법 암거래 규모 및 7년 만의 등록 가능성으로 기대감 형성.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['메모리', '자사주매입', '자사주소각']</t>
+          <t>['미프진', '주가조작', '식약처']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>72</v>
+        <v>2</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>004310</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>10780</v>
+        <v>1721000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+1.13%</t>
+          <t>'+1.83%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.29</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>86</v>
+        <v>800</v>
       </c>
       <c r="F11" t="n">
-        <v>55</v>
+        <v>480</v>
       </c>
       <c r="G11" t="n">
-        <v>142</v>
+        <v>1972</v>
       </c>
       <c r="H11" t="n">
-        <v>19.22</v>
+        <v>50.2</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>10660</v>
+        <v>1690000</v>
       </c>
       <c r="K11" t="n">
-        <v>10500</v>
+        <v>1686000</v>
       </c>
       <c r="L11" t="n">
-        <v>10900</v>
+        <v>1731000</v>
       </c>
       <c r="M11" t="n">
-        <v>10060</v>
+        <v>1686000</v>
       </c>
       <c r="N11" t="n">
-        <v>17.93</v>
+        <v>50.27</v>
       </c>
       <c r="O11" t="n">
-        <v>102059710870</v>
+        <v>2004067578000</v>
       </c>
       <c r="P11" t="n">
-        <v>22450</v>
+        <v>2987000</v>
       </c>
       <c r="Q11" t="n">
-        <v>1760</v>
+        <v>331500</v>
       </c>
       <c r="R11" t="n">
-        <v>-569000</v>
+        <v>-12000</v>
       </c>
       <c r="S11" t="n">
-        <v>1000</v>
+        <v>40000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>기대 거래량 충족 시 20% 상승 전망, 단기 급등 가능성 언급.</t>
+          <t>인텔 CEO의 메모리 수요 증가 전망과 함께 자사주 매입, 소각 기대감 언급. 금리 인상에도 불구하고 긍정적인 전망 제시.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['거래량', '상승', '차트']</t>
+          <t>['메모리', '자사주매입', '자사주소각']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>3</v>
+        <v>72</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10220</v>
+        <v>251250</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+0.99%</t>
+          <t>'+1.11%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.01</v>
       </c>
       <c r="E12" t="n">
-        <v>92</v>
+        <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>56</v>
+        <v>455</v>
       </c>
       <c r="G12" t="n">
-        <v>178</v>
+        <v>1903</v>
       </c>
       <c r="H12" t="n">
-        <v>0.67</v>
+        <v>46.56</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>10120</v>
+        <v>248500</v>
       </c>
       <c r="K12" t="n">
-        <v>10190</v>
+        <v>248000</v>
       </c>
       <c r="L12" t="n">
-        <v>10920</v>
+        <v>251500</v>
       </c>
       <c r="M12" t="n">
-        <v>9790</v>
+        <v>247500</v>
       </c>
       <c r="N12" t="n">
-        <v>0.6</v>
+        <v>46.57</v>
       </c>
       <c r="O12" t="n">
-        <v>93471425045</v>
+        <v>1175518098250</v>
       </c>
       <c r="P12" t="n">
-        <v>15960</v>
+        <v>374500</v>
       </c>
       <c r="Q12" t="n">
-        <v>3500</v>
+        <v>76700</v>
       </c>
       <c r="R12" t="n">
-        <v>-9000</v>
+        <v>-573000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>259000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>미프진 도입 공식화 관련 재료 소멸 가능성 및 주가 조작 의혹 제기, 단기 반등 기대.</t>
+          <t>금리 인상, 동복댐 물 부족, 정치적 논란 등 부정적 이슈와 함께 삼성전자 배당금 언급. 미국장 반도체 반등 및 인텔 CEO 발언으로 일부 기대감도 존재.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['미프진', '재료소멸', '주가조작']</t>
+          <t>['금리인상', '반도체', '배당금']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>2</v>
+        <v>107</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>004310</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>250750</v>
+        <v>13270</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+0.91%</t>
+          <t>'-0.23%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>800</v>
+        <v>49</v>
       </c>
       <c r="F13" t="n">
-        <v>454</v>
+        <v>40</v>
       </c>
       <c r="G13" t="n">
-        <v>1966</v>
+        <v>214</v>
       </c>
       <c r="H13" t="n">
-        <v>46.56</v>
+        <v>0</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,91 +1607,91 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>248500</v>
+        <v>13300</v>
       </c>
       <c r="K13" t="n">
-        <v>248000</v>
+        <v>13490</v>
       </c>
       <c r="L13" t="n">
-        <v>251500</v>
+        <v>13940</v>
       </c>
       <c r="M13" t="n">
-        <v>247500</v>
+        <v>13230</v>
       </c>
       <c r="N13" t="n">
-        <v>46.57</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>1128130716500</v>
+        <v>10687157255</v>
       </c>
       <c r="P13" t="n">
-        <v>374500</v>
+        <v>19380</v>
       </c>
       <c r="Q13" t="n">
-        <v>76700</v>
+        <v>3200</v>
       </c>
       <c r="R13" t="n">
-        <v>-573000</v>
+        <v>-22000</v>
       </c>
       <c r="S13" t="n">
-        <v>259000</v>
+        <v>3000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>금리인상 및 반도체 업황 관련 내용 혼재, 정치적 이슈와 연관된 부정적 의견 다수.</t>
+          <t>주가 하락 및 부진한 흐름에 대한 불만 토로, 영양가 없는 호재 언급. 투자 심리 위축.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['금리인상', '반도체', '업황']</t>
+          <t>['주가', '호재', '투자심리']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>107</v>
+        <v>54</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>13280</v>
+        <v>10550</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-0.15%</t>
+          <t>'-1.03%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="E14" t="n">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="F14" t="n">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="G14" t="n">
-        <v>210</v>
+        <v>151</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>19.22</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,327 +1699,327 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>13300</v>
+        <v>10660</v>
       </c>
       <c r="K14" t="n">
-        <v>13490</v>
+        <v>10500</v>
       </c>
       <c r="L14" t="n">
-        <v>13940</v>
+        <v>10900</v>
       </c>
       <c r="M14" t="n">
-        <v>13230</v>
+        <v>10060</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>17.93</v>
       </c>
       <c r="O14" t="n">
-        <v>10573704265</v>
+        <v>106391209945</v>
       </c>
       <c r="P14" t="n">
-        <v>19380</v>
+        <v>22450</v>
       </c>
       <c r="Q14" t="n">
-        <v>3200</v>
+        <v>1760</v>
       </c>
       <c r="R14" t="n">
-        <v>-22000</v>
+        <v>-569000</v>
       </c>
       <c r="S14" t="n">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>주가 하락 및 부진한 흐름에 대한 불만 토로, 영양가 없는 호재 언급. 투자 심리 위축.</t>
+          <t>의미 없는 투주에 따른 주가 급등 가능성 언급. 차트상 예술적인 움직임과 1000만주 거래량 시 20% 상승 전망.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['주가', '호재', '투자심리']</t>
+          <t>['투주', '거래량', '차트']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>54</v>
+        <v>3</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>한컴위드</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5210</v>
+        <v>8470</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-0.38%</t>
+          <t>'-1.63%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-1.39</v>
+        <v>-0.5</v>
       </c>
       <c r="E15" t="n">
-        <v>69</v>
+        <v>108</v>
       </c>
       <c r="F15" t="n">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="G15" t="n">
-        <v>165</v>
+        <v>335</v>
       </c>
       <c r="H15" t="n">
-        <v>1.29</v>
+        <v>26.66</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>5230</v>
+        <v>8610</v>
       </c>
       <c r="K15" t="n">
-        <v>5750</v>
+        <v>8600</v>
       </c>
       <c r="L15" t="n">
-        <v>5880</v>
+        <v>8610</v>
       </c>
       <c r="M15" t="n">
-        <v>5160</v>
+        <v>8430</v>
       </c>
       <c r="N15" t="n">
-        <v>2.68</v>
+        <v>27.16</v>
       </c>
       <c r="O15" t="n">
-        <v>54929468400</v>
+        <v>9311602925</v>
       </c>
       <c r="P15" t="n">
-        <v>8980</v>
+        <v>17950</v>
       </c>
       <c r="Q15" t="n">
-        <v>2795</v>
+        <v>8120</v>
       </c>
       <c r="R15" t="n">
-        <v>308000</v>
+        <v>-528000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>-36000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>미국 보안주 급등, 양자보안 구축 의무화 관련 기대감. 삼성과의 계약 규모에 대한 긍정적 전망 언급.</t>
+          <t>삼성디스플레이와 비교하며 실적 부진 지적, 대규모 부채 및 개미 투자자 매수세 우려.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['양자보안', '보안주', '계약']</t>
+          <t>['실적', '부채', '개미']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>054920</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>한컴위드</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>8470</v>
+        <v>5140</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-1.63%</t>
+          <t>'-1.72%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.5</v>
+        <v>-1.39</v>
       </c>
       <c r="E16" t="n">
-        <v>108</v>
+        <v>71</v>
       </c>
       <c r="F16" t="n">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="G16" t="n">
-        <v>335</v>
+        <v>165</v>
       </c>
       <c r="H16" t="n">
-        <v>26.66</v>
+        <v>1.29</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>8610</v>
+        <v>5230</v>
       </c>
       <c r="K16" t="n">
-        <v>8600</v>
+        <v>5750</v>
       </c>
       <c r="L16" t="n">
-        <v>8610</v>
+        <v>5880</v>
       </c>
       <c r="M16" t="n">
-        <v>8430</v>
+        <v>5140</v>
       </c>
       <c r="N16" t="n">
-        <v>27.16</v>
+        <v>2.68</v>
       </c>
       <c r="O16" t="n">
-        <v>9206304240</v>
+        <v>55505692525</v>
       </c>
       <c r="P16" t="n">
-        <v>17950</v>
+        <v>8980</v>
       </c>
       <c r="Q16" t="n">
-        <v>8120</v>
+        <v>2795</v>
       </c>
       <c r="R16" t="n">
-        <v>-528000</v>
+        <v>308000</v>
       </c>
       <c r="S16" t="n">
-        <v>-36000</v>
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>삼성디스플레이와 비교하며 실적 부진 지적, 대규모 부채 및 개미 투자자 매수세 우려.</t>
+          <t>미국 보안주 급등, 양자보안 구축 의무화 관련 기대감. 삼성과의 계약 규모에 대한 긍정적 전망 언급.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['실적', '부채', '개미']</t>
+          <t>['양자보안', '보안주', '계약']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>054920</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>83900</v>
+        <v>17100</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-2.67%</t>
+          <t>'-2.56%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.08</v>
+        <v>0.1</v>
       </c>
       <c r="E17" t="n">
-        <v>186</v>
+        <v>159</v>
       </c>
       <c r="F17" t="n">
-        <v>113</v>
+        <v>87</v>
       </c>
       <c r="G17" t="n">
-        <v>608</v>
+        <v>305</v>
       </c>
       <c r="H17" t="n">
-        <v>23.37</v>
+        <v>0.45</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>86200</v>
+        <v>17550</v>
       </c>
       <c r="K17" t="n">
-        <v>86200</v>
+        <v>17150</v>
       </c>
       <c r="L17" t="n">
-        <v>86300</v>
+        <v>18860</v>
       </c>
       <c r="M17" t="n">
-        <v>83800</v>
+        <v>16710</v>
       </c>
       <c r="N17" t="n">
-        <v>23.45</v>
+        <v>0.35</v>
       </c>
       <c r="O17" t="n">
-        <v>86482308100</v>
+        <v>153622561115</v>
       </c>
       <c r="P17" t="n">
-        <v>139200</v>
+        <v>30550</v>
       </c>
       <c r="Q17" t="n">
-        <v>57000</v>
+        <v>6100</v>
       </c>
       <c r="R17" t="n">
-        <v>-137000</v>
+        <v>-60000</v>
       </c>
       <c r="S17" t="n">
-        <v>-5000</v>
+        <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>웨스팅하우스 지분 인수 가능성에 대한 기대감과 공매도에 대한 언급이 있음.</t>
+          <t>미국 보안주 상승 및 상용화/매출 발생 기업 언급. 개미 털기 위한 주가 인위적 하락 의혹 및 변동성 심화.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['웨스팅하우스', '지분인수', '공매도']</t>
+          <t>['보안주', '개미털기', '주가 하락']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,38 +2028,38 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>16990</v>
+        <v>31500</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-3.19%</t>
+          <t>'-2.93%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.1</v>
+        <v>-0.34</v>
       </c>
       <c r="E18" t="n">
-        <v>157</v>
+        <v>196</v>
       </c>
       <c r="F18" t="n">
-        <v>87</v>
+        <v>121</v>
       </c>
       <c r="G18" t="n">
-        <v>302</v>
+        <v>1045</v>
       </c>
       <c r="H18" t="n">
-        <v>0.45</v>
+        <v>17.16</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,51 +2067,51 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>17550</v>
+        <v>32450</v>
       </c>
       <c r="K18" t="n">
-        <v>17150</v>
+        <v>32850</v>
       </c>
       <c r="L18" t="n">
-        <v>18860</v>
+        <v>32850</v>
       </c>
       <c r="M18" t="n">
-        <v>16710</v>
+        <v>30900</v>
       </c>
       <c r="N18" t="n">
-        <v>0.35</v>
+        <v>17.5</v>
       </c>
       <c r="O18" t="n">
-        <v>152439919285</v>
+        <v>7377573300</v>
       </c>
       <c r="P18" t="n">
-        <v>30550</v>
+        <v>69200</v>
       </c>
       <c r="Q18" t="n">
-        <v>6100</v>
+        <v>24150</v>
       </c>
       <c r="R18" t="n">
-        <v>-60000</v>
+        <v>-71000</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>미국 보안주 상승 및 상용화/매출 발생 기업 언급. 개미 털기 위한 주가 인위적 하락 의혹 및 변동성 심화.</t>
+          <t>간암 신약 실패 이력 기반 하방 베팅 의견. 유럽 담관암 신약 신청 시점에 대한 의문 제기 및 미국 승인 실패 시 주가 하락 가능성 언급.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['보안주', '개미털기', '주가 하락']</t>
+          <t>['간암', '담관암', '신약 신청']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,38 +2120,38 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>18440</v>
+        <v>83600</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-3.61%</t>
+          <t>'-3.02%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.11</v>
+        <v>-0.08</v>
       </c>
       <c r="E19" t="n">
-        <v>86</v>
+        <v>200</v>
       </c>
       <c r="F19" t="n">
-        <v>55</v>
+        <v>121</v>
       </c>
       <c r="G19" t="n">
-        <v>295</v>
+        <v>651</v>
       </c>
       <c r="H19" t="n">
-        <v>10.64</v>
+        <v>23.37</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,51 +2159,51 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>19130</v>
+        <v>86200</v>
       </c>
       <c r="K19" t="n">
-        <v>19160</v>
+        <v>86200</v>
       </c>
       <c r="L19" t="n">
-        <v>19340</v>
+        <v>86300</v>
       </c>
       <c r="M19" t="n">
-        <v>18330</v>
+        <v>83500</v>
       </c>
       <c r="N19" t="n">
-        <v>10.53</v>
+        <v>23.45</v>
       </c>
       <c r="O19" t="n">
-        <v>37450063845</v>
+        <v>92718711650</v>
       </c>
       <c r="P19" t="n">
-        <v>40350</v>
+        <v>139200</v>
       </c>
       <c r="Q19" t="n">
-        <v>3320</v>
+        <v>57000</v>
       </c>
       <c r="R19" t="n">
-        <v>-204000</v>
+        <v>-137000</v>
       </c>
       <c r="S19" t="n">
-        <v>-37000</v>
+        <v>-5000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>대차해지 운동 독려하며 공매도 세력과의 갈등 부각, 대형 계약 임박 및 주가 급등 기대.</t>
+          <t>웨스팅하우스 지분 인수 및 경영 참여 가능성에 대한 기대와 함께 공매도 세력의 압박 언급. 발표 전 상승 가능성과 함께 조심스러운 의견도 존재.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['대차해지', '공매도', '대형계약']</t>
+          <t>['웨스팅하우스', '지분인수', '공매도']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,90 +2212,90 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>31250</v>
+        <v>18490</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-3.70%</t>
+          <t>'-3.35%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.34</v>
+        <v>0.11</v>
       </c>
       <c r="E20" t="n">
-        <v>193</v>
+        <v>89</v>
       </c>
       <c r="F20" t="n">
-        <v>121</v>
+        <v>55</v>
       </c>
       <c r="G20" t="n">
-        <v>1027</v>
+        <v>299</v>
       </c>
       <c r="H20" t="n">
-        <v>17.16</v>
+        <v>10.64</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>32450</v>
+        <v>19130</v>
       </c>
       <c r="K20" t="n">
-        <v>32850</v>
+        <v>19160</v>
       </c>
       <c r="L20" t="n">
-        <v>32850</v>
+        <v>19340</v>
       </c>
       <c r="M20" t="n">
-        <v>30900</v>
+        <v>18330</v>
       </c>
       <c r="N20" t="n">
-        <v>17.5</v>
+        <v>10.53</v>
       </c>
       <c r="O20" t="n">
-        <v>6798095300</v>
+        <v>38073042290</v>
       </c>
       <c r="P20" t="n">
-        <v>69200</v>
+        <v>40350</v>
       </c>
       <c r="Q20" t="n">
-        <v>24150</v>
+        <v>3320</v>
       </c>
       <c r="R20" t="n">
-        <v>-71000</v>
+        <v>-204000</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>-37000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>간암 신약 실패 이력 기반 하방 베팅 의견. 유럽 담관암 신약 신청 시점에 대한 의문 제기 및 미국 승인 실패 시 주가 하락 가능성 언급.</t>
+          <t>대차해지 운동 독려하며 공매도 세력과의 갈등 부각, 대형 계약 임박 및 주가 급등 기대.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['간암', '담관암', '신약 신청']</t>
+          <t>['대차해지', '공매도', '대형계약']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>14180</v>
+        <v>13990</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-5.34%</t>
+          <t>'-6.61%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="F21" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G21" t="n">
-        <v>448</v>
+        <v>471</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -2352,13 +2352,13 @@
         <v>15580</v>
       </c>
       <c r="M21" t="n">
-        <v>14140</v>
+        <v>13990</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>24847806270</v>
+        <v>26514722655</v>
       </c>
       <c r="P21" t="n">
         <v>36200</v>
@@ -2374,16 +2374,16 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>국제유가 상승 및 지정학적 리스크 부각, 단기 급등 가능성 언급하나 차익 실현 및 급락 우려 상존.</t>
+          <t>사우디발 국제유가 상승 및 미장 에너지주 폭등에 따른 흥구석유 급등 기대감. 비축유 문제 및 이란 관련 지정학적 리스크 부각.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['국제유가', '지정학적리스크', '급등']</t>
+          <t>['국제유가', '에너지주', '지정학적리스크']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2407,11 +2407,11 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5870</v>
+        <v>5890</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-6.97%</t>
+          <t>'-6.66%</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -2424,7 +2424,7 @@
         <v>48</v>
       </c>
       <c r="G22" t="n">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H22" t="n">
         <v>0.98</v>
@@ -2450,7 +2450,7 @@
         <v>3.02</v>
       </c>
       <c r="O22" t="n">
-        <v>39467572245</v>
+        <v>39650010505</v>
       </c>
       <c r="P22" t="n">
         <v>11370</v>
